--- a/Shafi Goth/Student Information.xlsx
+++ b/Shafi Goth/Student Information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Shafi Goth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E74B88-470D-493D-AE54-C0C9A3363EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27C56CA-C02A-471F-A660-BEF1DCBE8F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3647,7 +3647,16 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3656,16 +3665,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3722,11 +3725,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3734,8 +3734,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3796,9 +3799,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4101,120 +4101,120 @@
     <row r="1" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C1" s="44"/>
       <c r="D1" s="44"/>
-      <c r="E1" s="111" t="s">
+      <c r="E1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
       <c r="U1" s="44"/>
       <c r="V1" s="44"/>
     </row>
     <row r="2" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C2" s="44"/>
       <c r="D2" s="44"/>
-      <c r="E2" s="110" t="s">
+      <c r="E2" s="114" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
-      <c r="T2" s="111"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
+      <c r="S2" s="113"/>
+      <c r="T2" s="113"/>
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
     </row>
     <row r="3" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
-      <c r="E3" s="110" t="s">
+      <c r="E3" s="114" t="s">
         <v>292</v>
       </c>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="113"/>
+      <c r="Q3" s="113"/>
+      <c r="R3" s="113"/>
+      <c r="S3" s="113"/>
+      <c r="T3" s="113"/>
       <c r="U3" s="44"/>
       <c r="V3" s="44"/>
     </row>
     <row r="4" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C4" s="44"/>
       <c r="D4" s="44"/>
-      <c r="E4" s="110" t="s">
+      <c r="E4" s="114" t="s">
         <v>296</v>
       </c>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111"/>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111"/>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113"/>
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
     </row>
     <row r="5" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C5" s="44"/>
       <c r="D5" s="44"/>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="114" t="s">
         <v>293</v>
       </c>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-      <c r="R5" s="111"/>
-      <c r="S5" s="111"/>
-      <c r="T5" s="111"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
       <c r="U5" s="44"/>
       <c r="V5" s="44"/>
     </row>
@@ -5485,48 +5485,48 @@
     <row r="30" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C30" s="44"/>
       <c r="D30" s="52"/>
-      <c r="E30" s="107" t="s">
+      <c r="E30" s="108" t="s">
         <v>297</v>
       </c>
-      <c r="F30" s="112"/>
-      <c r="G30" s="112"/>
-      <c r="H30" s="112"/>
-      <c r="I30" s="112"/>
-      <c r="J30" s="112"/>
-      <c r="K30" s="112"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="112"/>
-      <c r="R30" s="112"/>
-      <c r="S30" s="112"/>
-      <c r="T30" s="113"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="109"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="109"/>
+      <c r="J30" s="109"/>
+      <c r="K30" s="109"/>
+      <c r="L30" s="109"/>
+      <c r="M30" s="109"/>
+      <c r="N30" s="109"/>
+      <c r="O30" s="109"/>
+      <c r="P30" s="109"/>
+      <c r="Q30" s="109"/>
+      <c r="R30" s="109"/>
+      <c r="S30" s="109"/>
+      <c r="T30" s="110"/>
       <c r="U30" s="44"/>
       <c r="V30" s="44"/>
     </row>
     <row r="31" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C31" s="44"/>
       <c r="D31" s="52"/>
-      <c r="E31" s="112" t="s">
+      <c r="E31" s="109" t="s">
         <v>294</v>
       </c>
-      <c r="F31" s="108"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="108"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="108"/>
-      <c r="K31" s="108"/>
-      <c r="L31" s="108"/>
-      <c r="M31" s="108"/>
-      <c r="N31" s="108"/>
-      <c r="O31" s="108"/>
-      <c r="P31" s="108"/>
-      <c r="Q31" s="108"/>
-      <c r="R31" s="108"/>
-      <c r="S31" s="108"/>
-      <c r="T31" s="109"/>
+      <c r="F31" s="111"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="111"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="111"/>
+      <c r="N31" s="111"/>
+      <c r="O31" s="111"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="111"/>
+      <c r="S31" s="111"/>
+      <c r="T31" s="112"/>
       <c r="U31" s="44"/>
       <c r="V31" s="44"/>
     </row>
@@ -6257,48 +6257,48 @@
     <row r="46" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C46" s="44"/>
       <c r="D46" s="44"/>
-      <c r="E46" s="107" t="s">
+      <c r="E46" s="108" t="s">
         <v>298</v>
       </c>
-      <c r="F46" s="108"/>
-      <c r="G46" s="108"/>
-      <c r="H46" s="108"/>
-      <c r="I46" s="108"/>
-      <c r="J46" s="108"/>
-      <c r="K46" s="108"/>
-      <c r="L46" s="108"/>
-      <c r="M46" s="108"/>
-      <c r="N46" s="108"/>
-      <c r="O46" s="108"/>
-      <c r="P46" s="108"/>
-      <c r="Q46" s="108"/>
-      <c r="R46" s="108"/>
-      <c r="S46" s="108"/>
-      <c r="T46" s="109"/>
+      <c r="F46" s="111"/>
+      <c r="G46" s="111"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="111"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="111"/>
+      <c r="L46" s="111"/>
+      <c r="M46" s="111"/>
+      <c r="N46" s="111"/>
+      <c r="O46" s="111"/>
+      <c r="P46" s="111"/>
+      <c r="Q46" s="111"/>
+      <c r="R46" s="111"/>
+      <c r="S46" s="111"/>
+      <c r="T46" s="112"/>
       <c r="U46" s="44"/>
       <c r="V46" s="44"/>
     </row>
     <row r="47" spans="3:22" ht="21" x14ac:dyDescent="0.35">
       <c r="C47" s="44"/>
       <c r="D47" s="44"/>
-      <c r="E47" s="107" t="s">
+      <c r="E47" s="108" t="s">
         <v>295</v>
       </c>
-      <c r="F47" s="108"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="108"/>
-      <c r="I47" s="108"/>
-      <c r="J47" s="108"/>
-      <c r="K47" s="108"/>
-      <c r="L47" s="108"/>
-      <c r="M47" s="108"/>
-      <c r="N47" s="108"/>
-      <c r="O47" s="108"/>
-      <c r="P47" s="108"/>
-      <c r="Q47" s="108"/>
-      <c r="R47" s="108"/>
-      <c r="S47" s="108"/>
-      <c r="T47" s="109"/>
+      <c r="F47" s="111"/>
+      <c r="G47" s="111"/>
+      <c r="H47" s="111"/>
+      <c r="I47" s="111"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="111"/>
+      <c r="L47" s="111"/>
+      <c r="M47" s="111"/>
+      <c r="N47" s="111"/>
+      <c r="O47" s="111"/>
+      <c r="P47" s="111"/>
+      <c r="Q47" s="111"/>
+      <c r="R47" s="111"/>
+      <c r="S47" s="111"/>
+      <c r="T47" s="112"/>
       <c r="U47" s="44"/>
       <c r="V47" s="44"/>
     </row>
@@ -7191,104 +7191,104 @@
       <c r="V64" s="44"/>
     </row>
     <row r="66" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E66" s="111" t="s">
+      <c r="E66" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="F66" s="111"/>
-      <c r="G66" s="111"/>
-      <c r="H66" s="111"/>
-      <c r="I66" s="111"/>
-      <c r="J66" s="111"/>
-      <c r="K66" s="111"/>
-      <c r="L66" s="111"/>
-      <c r="M66" s="111"/>
-      <c r="N66" s="111"/>
-      <c r="O66" s="111"/>
-      <c r="P66" s="111"/>
-      <c r="Q66" s="111"/>
-      <c r="R66" s="111"/>
-      <c r="S66" s="111"/>
-      <c r="T66" s="111"/>
+      <c r="F66" s="113"/>
+      <c r="G66" s="113"/>
+      <c r="H66" s="113"/>
+      <c r="I66" s="113"/>
+      <c r="J66" s="113"/>
+      <c r="K66" s="113"/>
+      <c r="L66" s="113"/>
+      <c r="M66" s="113"/>
+      <c r="N66" s="113"/>
+      <c r="O66" s="113"/>
+      <c r="P66" s="113"/>
+      <c r="Q66" s="113"/>
+      <c r="R66" s="113"/>
+      <c r="S66" s="113"/>
+      <c r="T66" s="113"/>
     </row>
     <row r="67" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E67" s="110" t="s">
+      <c r="E67" s="114" t="s">
         <v>291</v>
       </c>
-      <c r="F67" s="111"/>
-      <c r="G67" s="111"/>
-      <c r="H67" s="111"/>
-      <c r="I67" s="111"/>
-      <c r="J67" s="111"/>
-      <c r="K67" s="111"/>
-      <c r="L67" s="111"/>
-      <c r="M67" s="111"/>
-      <c r="N67" s="111"/>
-      <c r="O67" s="111"/>
-      <c r="P67" s="111"/>
-      <c r="Q67" s="111"/>
-      <c r="R67" s="111"/>
-      <c r="S67" s="111"/>
-      <c r="T67" s="111"/>
+      <c r="F67" s="113"/>
+      <c r="G67" s="113"/>
+      <c r="H67" s="113"/>
+      <c r="I67" s="113"/>
+      <c r="J67" s="113"/>
+      <c r="K67" s="113"/>
+      <c r="L67" s="113"/>
+      <c r="M67" s="113"/>
+      <c r="N67" s="113"/>
+      <c r="O67" s="113"/>
+      <c r="P67" s="113"/>
+      <c r="Q67" s="113"/>
+      <c r="R67" s="113"/>
+      <c r="S67" s="113"/>
+      <c r="T67" s="113"/>
     </row>
     <row r="68" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E68" s="110" t="s">
+      <c r="E68" s="114" t="s">
         <v>292</v>
       </c>
-      <c r="F68" s="111"/>
-      <c r="G68" s="111"/>
-      <c r="H68" s="111"/>
-      <c r="I68" s="111"/>
-      <c r="J68" s="111"/>
-      <c r="K68" s="111"/>
-      <c r="L68" s="111"/>
-      <c r="M68" s="111"/>
-      <c r="N68" s="111"/>
-      <c r="O68" s="111"/>
-      <c r="P68" s="111"/>
-      <c r="Q68" s="111"/>
-      <c r="R68" s="111"/>
-      <c r="S68" s="111"/>
-      <c r="T68" s="111"/>
+      <c r="F68" s="113"/>
+      <c r="G68" s="113"/>
+      <c r="H68" s="113"/>
+      <c r="I68" s="113"/>
+      <c r="J68" s="113"/>
+      <c r="K68" s="113"/>
+      <c r="L68" s="113"/>
+      <c r="M68" s="113"/>
+      <c r="N68" s="113"/>
+      <c r="O68" s="113"/>
+      <c r="P68" s="113"/>
+      <c r="Q68" s="113"/>
+      <c r="R68" s="113"/>
+      <c r="S68" s="113"/>
+      <c r="T68" s="113"/>
     </row>
     <row r="69" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E69" s="110" t="s">
+      <c r="E69" s="114" t="s">
         <v>312</v>
       </c>
-      <c r="F69" s="111"/>
-      <c r="G69" s="111"/>
-      <c r="H69" s="111"/>
-      <c r="I69" s="111"/>
-      <c r="J69" s="111"/>
-      <c r="K69" s="111"/>
-      <c r="L69" s="111"/>
-      <c r="M69" s="111"/>
-      <c r="N69" s="111"/>
-      <c r="O69" s="111"/>
-      <c r="P69" s="111"/>
-      <c r="Q69" s="111"/>
-      <c r="R69" s="111"/>
-      <c r="S69" s="111"/>
-      <c r="T69" s="111"/>
+      <c r="F69" s="113"/>
+      <c r="G69" s="113"/>
+      <c r="H69" s="113"/>
+      <c r="I69" s="113"/>
+      <c r="J69" s="113"/>
+      <c r="K69" s="113"/>
+      <c r="L69" s="113"/>
+      <c r="M69" s="113"/>
+      <c r="N69" s="113"/>
+      <c r="O69" s="113"/>
+      <c r="P69" s="113"/>
+      <c r="Q69" s="113"/>
+      <c r="R69" s="113"/>
+      <c r="S69" s="113"/>
+      <c r="T69" s="113"/>
     </row>
     <row r="70" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E70" s="110" t="s">
+      <c r="E70" s="114" t="s">
         <v>293</v>
       </c>
-      <c r="F70" s="111"/>
-      <c r="G70" s="111"/>
-      <c r="H70" s="111"/>
-      <c r="I70" s="111"/>
-      <c r="J70" s="111"/>
-      <c r="K70" s="111"/>
-      <c r="L70" s="111"/>
-      <c r="M70" s="111"/>
-      <c r="N70" s="111"/>
-      <c r="O70" s="111"/>
-      <c r="P70" s="111"/>
-      <c r="Q70" s="111"/>
-      <c r="R70" s="111"/>
-      <c r="S70" s="111"/>
-      <c r="T70" s="111"/>
+      <c r="F70" s="113"/>
+      <c r="G70" s="113"/>
+      <c r="H70" s="113"/>
+      <c r="I70" s="113"/>
+      <c r="J70" s="113"/>
+      <c r="K70" s="113"/>
+      <c r="L70" s="113"/>
+      <c r="M70" s="113"/>
+      <c r="N70" s="113"/>
+      <c r="O70" s="113"/>
+      <c r="P70" s="113"/>
+      <c r="Q70" s="113"/>
+      <c r="R70" s="113"/>
+      <c r="S70" s="113"/>
+      <c r="T70" s="113"/>
     </row>
     <row r="71" spans="5:20" ht="21" x14ac:dyDescent="0.35">
       <c r="E71" s="63" t="s">
@@ -8459,44 +8459,44 @@
       </c>
     </row>
     <row r="95" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E95" s="107" t="s">
+      <c r="E95" s="108" t="s">
         <v>312</v>
       </c>
-      <c r="F95" s="112"/>
-      <c r="G95" s="112"/>
-      <c r="H95" s="112"/>
-      <c r="I95" s="112"/>
-      <c r="J95" s="112"/>
-      <c r="K95" s="112"/>
-      <c r="L95" s="112"/>
-      <c r="M95" s="112"/>
-      <c r="N95" s="112"/>
-      <c r="O95" s="112"/>
-      <c r="P95" s="112"/>
-      <c r="Q95" s="112"/>
-      <c r="R95" s="112"/>
-      <c r="S95" s="112"/>
-      <c r="T95" s="113"/>
+      <c r="F95" s="109"/>
+      <c r="G95" s="109"/>
+      <c r="H95" s="109"/>
+      <c r="I95" s="109"/>
+      <c r="J95" s="109"/>
+      <c r="K95" s="109"/>
+      <c r="L95" s="109"/>
+      <c r="M95" s="109"/>
+      <c r="N95" s="109"/>
+      <c r="O95" s="109"/>
+      <c r="P95" s="109"/>
+      <c r="Q95" s="109"/>
+      <c r="R95" s="109"/>
+      <c r="S95" s="109"/>
+      <c r="T95" s="110"/>
     </row>
     <row r="96" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E96" s="112" t="s">
+      <c r="E96" s="109" t="s">
         <v>294</v>
       </c>
-      <c r="F96" s="108"/>
-      <c r="G96" s="108"/>
-      <c r="H96" s="108"/>
-      <c r="I96" s="108"/>
-      <c r="J96" s="108"/>
-      <c r="K96" s="108"/>
-      <c r="L96" s="108"/>
-      <c r="M96" s="108"/>
-      <c r="N96" s="108"/>
-      <c r="O96" s="108"/>
-      <c r="P96" s="108"/>
-      <c r="Q96" s="108"/>
-      <c r="R96" s="108"/>
-      <c r="S96" s="108"/>
-      <c r="T96" s="109"/>
+      <c r="F96" s="111"/>
+      <c r="G96" s="111"/>
+      <c r="H96" s="111"/>
+      <c r="I96" s="111"/>
+      <c r="J96" s="111"/>
+      <c r="K96" s="111"/>
+      <c r="L96" s="111"/>
+      <c r="M96" s="111"/>
+      <c r="N96" s="111"/>
+      <c r="O96" s="111"/>
+      <c r="P96" s="111"/>
+      <c r="Q96" s="111"/>
+      <c r="R96" s="111"/>
+      <c r="S96" s="111"/>
+      <c r="T96" s="112"/>
     </row>
     <row r="97" spans="5:20" ht="21" x14ac:dyDescent="0.25">
       <c r="E97" s="63" t="s">
@@ -9167,44 +9167,44 @@
       </c>
     </row>
     <row r="111" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E111" s="107" t="s">
+      <c r="E111" s="108" t="s">
         <v>313</v>
       </c>
-      <c r="F111" s="108"/>
-      <c r="G111" s="108"/>
-      <c r="H111" s="108"/>
-      <c r="I111" s="108"/>
-      <c r="J111" s="108"/>
-      <c r="K111" s="108"/>
-      <c r="L111" s="108"/>
-      <c r="M111" s="108"/>
-      <c r="N111" s="108"/>
-      <c r="O111" s="108"/>
-      <c r="P111" s="108"/>
-      <c r="Q111" s="108"/>
-      <c r="R111" s="108"/>
-      <c r="S111" s="108"/>
-      <c r="T111" s="109"/>
+      <c r="F111" s="111"/>
+      <c r="G111" s="111"/>
+      <c r="H111" s="111"/>
+      <c r="I111" s="111"/>
+      <c r="J111" s="111"/>
+      <c r="K111" s="111"/>
+      <c r="L111" s="111"/>
+      <c r="M111" s="111"/>
+      <c r="N111" s="111"/>
+      <c r="O111" s="111"/>
+      <c r="P111" s="111"/>
+      <c r="Q111" s="111"/>
+      <c r="R111" s="111"/>
+      <c r="S111" s="111"/>
+      <c r="T111" s="112"/>
     </row>
     <row r="112" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E112" s="107" t="s">
+      <c r="E112" s="108" t="s">
         <v>295</v>
       </c>
-      <c r="F112" s="108"/>
-      <c r="G112" s="108"/>
-      <c r="H112" s="108"/>
-      <c r="I112" s="108"/>
-      <c r="J112" s="108"/>
-      <c r="K112" s="108"/>
-      <c r="L112" s="108"/>
-      <c r="M112" s="108"/>
-      <c r="N112" s="108"/>
-      <c r="O112" s="108"/>
-      <c r="P112" s="108"/>
-      <c r="Q112" s="108"/>
-      <c r="R112" s="108"/>
-      <c r="S112" s="108"/>
-      <c r="T112" s="109"/>
+      <c r="F112" s="111"/>
+      <c r="G112" s="111"/>
+      <c r="H112" s="111"/>
+      <c r="I112" s="111"/>
+      <c r="J112" s="111"/>
+      <c r="K112" s="111"/>
+      <c r="L112" s="111"/>
+      <c r="M112" s="111"/>
+      <c r="N112" s="111"/>
+      <c r="O112" s="111"/>
+      <c r="P112" s="111"/>
+      <c r="Q112" s="111"/>
+      <c r="R112" s="111"/>
+      <c r="S112" s="111"/>
+      <c r="T112" s="112"/>
     </row>
     <row r="113" spans="5:20" ht="21" x14ac:dyDescent="0.25">
       <c r="E113" s="63" t="s">
@@ -10027,104 +10027,104 @@
       </c>
     </row>
     <row r="131" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E131" s="111" t="s">
+      <c r="E131" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="F131" s="111"/>
-      <c r="G131" s="111"/>
-      <c r="H131" s="111"/>
-      <c r="I131" s="111"/>
-      <c r="J131" s="111"/>
-      <c r="K131" s="111"/>
-      <c r="L131" s="111"/>
-      <c r="M131" s="111"/>
-      <c r="N131" s="111"/>
-      <c r="O131" s="111"/>
-      <c r="P131" s="111"/>
-      <c r="Q131" s="111"/>
-      <c r="R131" s="111"/>
-      <c r="S131" s="111"/>
-      <c r="T131" s="111"/>
+      <c r="F131" s="113"/>
+      <c r="G131" s="113"/>
+      <c r="H131" s="113"/>
+      <c r="I131" s="113"/>
+      <c r="J131" s="113"/>
+      <c r="K131" s="113"/>
+      <c r="L131" s="113"/>
+      <c r="M131" s="113"/>
+      <c r="N131" s="113"/>
+      <c r="O131" s="113"/>
+      <c r="P131" s="113"/>
+      <c r="Q131" s="113"/>
+      <c r="R131" s="113"/>
+      <c r="S131" s="113"/>
+      <c r="T131" s="113"/>
     </row>
     <row r="132" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E132" s="110" t="s">
+      <c r="E132" s="114" t="s">
         <v>291</v>
       </c>
-      <c r="F132" s="111"/>
-      <c r="G132" s="111"/>
-      <c r="H132" s="111"/>
-      <c r="I132" s="111"/>
-      <c r="J132" s="111"/>
-      <c r="K132" s="111"/>
-      <c r="L132" s="111"/>
-      <c r="M132" s="111"/>
-      <c r="N132" s="111"/>
-      <c r="O132" s="111"/>
-      <c r="P132" s="111"/>
-      <c r="Q132" s="111"/>
-      <c r="R132" s="111"/>
-      <c r="S132" s="111"/>
-      <c r="T132" s="111"/>
+      <c r="F132" s="113"/>
+      <c r="G132" s="113"/>
+      <c r="H132" s="113"/>
+      <c r="I132" s="113"/>
+      <c r="J132" s="113"/>
+      <c r="K132" s="113"/>
+      <c r="L132" s="113"/>
+      <c r="M132" s="113"/>
+      <c r="N132" s="113"/>
+      <c r="O132" s="113"/>
+      <c r="P132" s="113"/>
+      <c r="Q132" s="113"/>
+      <c r="R132" s="113"/>
+      <c r="S132" s="113"/>
+      <c r="T132" s="113"/>
     </row>
     <row r="133" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E133" s="110" t="s">
+      <c r="E133" s="114" t="s">
         <v>292</v>
       </c>
-      <c r="F133" s="111"/>
-      <c r="G133" s="111"/>
-      <c r="H133" s="111"/>
-      <c r="I133" s="111"/>
-      <c r="J133" s="111"/>
-      <c r="K133" s="111"/>
-      <c r="L133" s="111"/>
-      <c r="M133" s="111"/>
-      <c r="N133" s="111"/>
-      <c r="O133" s="111"/>
-      <c r="P133" s="111"/>
-      <c r="Q133" s="111"/>
-      <c r="R133" s="111"/>
-      <c r="S133" s="111"/>
-      <c r="T133" s="111"/>
+      <c r="F133" s="113"/>
+      <c r="G133" s="113"/>
+      <c r="H133" s="113"/>
+      <c r="I133" s="113"/>
+      <c r="J133" s="113"/>
+      <c r="K133" s="113"/>
+      <c r="L133" s="113"/>
+      <c r="M133" s="113"/>
+      <c r="N133" s="113"/>
+      <c r="O133" s="113"/>
+      <c r="P133" s="113"/>
+      <c r="Q133" s="113"/>
+      <c r="R133" s="113"/>
+      <c r="S133" s="113"/>
+      <c r="T133" s="113"/>
     </row>
     <row r="134" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E134" s="110" t="s">
+      <c r="E134" s="114" t="s">
         <v>316</v>
       </c>
-      <c r="F134" s="111"/>
-      <c r="G134" s="111"/>
-      <c r="H134" s="111"/>
-      <c r="I134" s="111"/>
-      <c r="J134" s="111"/>
-      <c r="K134" s="111"/>
-      <c r="L134" s="111"/>
-      <c r="M134" s="111"/>
-      <c r="N134" s="111"/>
-      <c r="O134" s="111"/>
-      <c r="P134" s="111"/>
-      <c r="Q134" s="111"/>
-      <c r="R134" s="111"/>
-      <c r="S134" s="111"/>
-      <c r="T134" s="111"/>
+      <c r="F134" s="113"/>
+      <c r="G134" s="113"/>
+      <c r="H134" s="113"/>
+      <c r="I134" s="113"/>
+      <c r="J134" s="113"/>
+      <c r="K134" s="113"/>
+      <c r="L134" s="113"/>
+      <c r="M134" s="113"/>
+      <c r="N134" s="113"/>
+      <c r="O134" s="113"/>
+      <c r="P134" s="113"/>
+      <c r="Q134" s="113"/>
+      <c r="R134" s="113"/>
+      <c r="S134" s="113"/>
+      <c r="T134" s="113"/>
     </row>
     <row r="135" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E135" s="110" t="s">
+      <c r="E135" s="114" t="s">
         <v>293</v>
       </c>
-      <c r="F135" s="111"/>
-      <c r="G135" s="111"/>
-      <c r="H135" s="111"/>
-      <c r="I135" s="111"/>
-      <c r="J135" s="111"/>
-      <c r="K135" s="111"/>
-      <c r="L135" s="111"/>
-      <c r="M135" s="111"/>
-      <c r="N135" s="111"/>
-      <c r="O135" s="111"/>
-      <c r="P135" s="111"/>
-      <c r="Q135" s="111"/>
-      <c r="R135" s="111"/>
-      <c r="S135" s="111"/>
-      <c r="T135" s="111"/>
+      <c r="F135" s="113"/>
+      <c r="G135" s="113"/>
+      <c r="H135" s="113"/>
+      <c r="I135" s="113"/>
+      <c r="J135" s="113"/>
+      <c r="K135" s="113"/>
+      <c r="L135" s="113"/>
+      <c r="M135" s="113"/>
+      <c r="N135" s="113"/>
+      <c r="O135" s="113"/>
+      <c r="P135" s="113"/>
+      <c r="Q135" s="113"/>
+      <c r="R135" s="113"/>
+      <c r="S135" s="113"/>
+      <c r="T135" s="113"/>
     </row>
     <row r="136" spans="5:20" ht="21" x14ac:dyDescent="0.35">
       <c r="E136" s="63" t="s">
@@ -11295,44 +11295,44 @@
       </c>
     </row>
     <row r="160" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E160" s="107" t="s">
+      <c r="E160" s="108" t="s">
         <v>316</v>
       </c>
-      <c r="F160" s="112"/>
-      <c r="G160" s="112"/>
-      <c r="H160" s="112"/>
-      <c r="I160" s="112"/>
-      <c r="J160" s="112"/>
-      <c r="K160" s="112"/>
-      <c r="L160" s="112"/>
-      <c r="M160" s="112"/>
-      <c r="N160" s="112"/>
-      <c r="O160" s="112"/>
-      <c r="P160" s="112"/>
-      <c r="Q160" s="112"/>
-      <c r="R160" s="112"/>
-      <c r="S160" s="112"/>
-      <c r="T160" s="113"/>
+      <c r="F160" s="109"/>
+      <c r="G160" s="109"/>
+      <c r="H160" s="109"/>
+      <c r="I160" s="109"/>
+      <c r="J160" s="109"/>
+      <c r="K160" s="109"/>
+      <c r="L160" s="109"/>
+      <c r="M160" s="109"/>
+      <c r="N160" s="109"/>
+      <c r="O160" s="109"/>
+      <c r="P160" s="109"/>
+      <c r="Q160" s="109"/>
+      <c r="R160" s="109"/>
+      <c r="S160" s="109"/>
+      <c r="T160" s="110"/>
     </row>
     <row r="161" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E161" s="112" t="s">
+      <c r="E161" s="109" t="s">
         <v>294</v>
       </c>
-      <c r="F161" s="108"/>
-      <c r="G161" s="108"/>
-      <c r="H161" s="108"/>
-      <c r="I161" s="108"/>
-      <c r="J161" s="108"/>
-      <c r="K161" s="108"/>
-      <c r="L161" s="108"/>
-      <c r="M161" s="108"/>
-      <c r="N161" s="108"/>
-      <c r="O161" s="108"/>
-      <c r="P161" s="108"/>
-      <c r="Q161" s="108"/>
-      <c r="R161" s="108"/>
-      <c r="S161" s="108"/>
-      <c r="T161" s="109"/>
+      <c r="F161" s="111"/>
+      <c r="G161" s="111"/>
+      <c r="H161" s="111"/>
+      <c r="I161" s="111"/>
+      <c r="J161" s="111"/>
+      <c r="K161" s="111"/>
+      <c r="L161" s="111"/>
+      <c r="M161" s="111"/>
+      <c r="N161" s="111"/>
+      <c r="O161" s="111"/>
+      <c r="P161" s="111"/>
+      <c r="Q161" s="111"/>
+      <c r="R161" s="111"/>
+      <c r="S161" s="111"/>
+      <c r="T161" s="112"/>
     </row>
     <row r="162" spans="5:20" ht="21" x14ac:dyDescent="0.25">
       <c r="E162" s="63" t="s">
@@ -12003,44 +12003,44 @@
       </c>
     </row>
     <row r="176" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E176" s="107" t="s">
+      <c r="E176" s="108" t="s">
         <v>317</v>
       </c>
-      <c r="F176" s="108"/>
-      <c r="G176" s="108"/>
-      <c r="H176" s="108"/>
-      <c r="I176" s="108"/>
-      <c r="J176" s="108"/>
-      <c r="K176" s="108"/>
-      <c r="L176" s="108"/>
-      <c r="M176" s="108"/>
-      <c r="N176" s="108"/>
-      <c r="O176" s="108"/>
-      <c r="P176" s="108"/>
-      <c r="Q176" s="108"/>
-      <c r="R176" s="108"/>
-      <c r="S176" s="108"/>
-      <c r="T176" s="109"/>
+      <c r="F176" s="111"/>
+      <c r="G176" s="111"/>
+      <c r="H176" s="111"/>
+      <c r="I176" s="111"/>
+      <c r="J176" s="111"/>
+      <c r="K176" s="111"/>
+      <c r="L176" s="111"/>
+      <c r="M176" s="111"/>
+      <c r="N176" s="111"/>
+      <c r="O176" s="111"/>
+      <c r="P176" s="111"/>
+      <c r="Q176" s="111"/>
+      <c r="R176" s="111"/>
+      <c r="S176" s="111"/>
+      <c r="T176" s="112"/>
     </row>
     <row r="177" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E177" s="107" t="s">
+      <c r="E177" s="108" t="s">
         <v>295</v>
       </c>
-      <c r="F177" s="108"/>
-      <c r="G177" s="108"/>
-      <c r="H177" s="108"/>
-      <c r="I177" s="108"/>
-      <c r="J177" s="108"/>
-      <c r="K177" s="108"/>
-      <c r="L177" s="108"/>
-      <c r="M177" s="108"/>
-      <c r="N177" s="108"/>
-      <c r="O177" s="108"/>
-      <c r="P177" s="108"/>
-      <c r="Q177" s="108"/>
-      <c r="R177" s="108"/>
-      <c r="S177" s="108"/>
-      <c r="T177" s="109"/>
+      <c r="F177" s="111"/>
+      <c r="G177" s="111"/>
+      <c r="H177" s="111"/>
+      <c r="I177" s="111"/>
+      <c r="J177" s="111"/>
+      <c r="K177" s="111"/>
+      <c r="L177" s="111"/>
+      <c r="M177" s="111"/>
+      <c r="N177" s="111"/>
+      <c r="O177" s="111"/>
+      <c r="P177" s="111"/>
+      <c r="Q177" s="111"/>
+      <c r="R177" s="111"/>
+      <c r="S177" s="111"/>
+      <c r="T177" s="112"/>
     </row>
     <row r="178" spans="5:20" ht="21" x14ac:dyDescent="0.25">
       <c r="E178" s="63" t="s">
@@ -12863,104 +12863,104 @@
       </c>
     </row>
     <row r="196" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E196" s="111" t="s">
+      <c r="E196" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="F196" s="111"/>
-      <c r="G196" s="111"/>
-      <c r="H196" s="111"/>
-      <c r="I196" s="111"/>
-      <c r="J196" s="111"/>
-      <c r="K196" s="111"/>
-      <c r="L196" s="111"/>
-      <c r="M196" s="111"/>
-      <c r="N196" s="111"/>
-      <c r="O196" s="111"/>
-      <c r="P196" s="111"/>
-      <c r="Q196" s="111"/>
-      <c r="R196" s="111"/>
-      <c r="S196" s="111"/>
-      <c r="T196" s="111"/>
+      <c r="F196" s="113"/>
+      <c r="G196" s="113"/>
+      <c r="H196" s="113"/>
+      <c r="I196" s="113"/>
+      <c r="J196" s="113"/>
+      <c r="K196" s="113"/>
+      <c r="L196" s="113"/>
+      <c r="M196" s="113"/>
+      <c r="N196" s="113"/>
+      <c r="O196" s="113"/>
+      <c r="P196" s="113"/>
+      <c r="Q196" s="113"/>
+      <c r="R196" s="113"/>
+      <c r="S196" s="113"/>
+      <c r="T196" s="113"/>
     </row>
     <row r="197" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E197" s="110" t="s">
+      <c r="E197" s="114" t="s">
         <v>291</v>
       </c>
-      <c r="F197" s="111"/>
-      <c r="G197" s="111"/>
-      <c r="H197" s="111"/>
-      <c r="I197" s="111"/>
-      <c r="J197" s="111"/>
-      <c r="K197" s="111"/>
-      <c r="L197" s="111"/>
-      <c r="M197" s="111"/>
-      <c r="N197" s="111"/>
-      <c r="O197" s="111"/>
-      <c r="P197" s="111"/>
-      <c r="Q197" s="111"/>
-      <c r="R197" s="111"/>
-      <c r="S197" s="111"/>
-      <c r="T197" s="111"/>
+      <c r="F197" s="113"/>
+      <c r="G197" s="113"/>
+      <c r="H197" s="113"/>
+      <c r="I197" s="113"/>
+      <c r="J197" s="113"/>
+      <c r="K197" s="113"/>
+      <c r="L197" s="113"/>
+      <c r="M197" s="113"/>
+      <c r="N197" s="113"/>
+      <c r="O197" s="113"/>
+      <c r="P197" s="113"/>
+      <c r="Q197" s="113"/>
+      <c r="R197" s="113"/>
+      <c r="S197" s="113"/>
+      <c r="T197" s="113"/>
     </row>
     <row r="198" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E198" s="110" t="s">
+      <c r="E198" s="114" t="s">
         <v>292</v>
       </c>
-      <c r="F198" s="111"/>
-      <c r="G198" s="111"/>
-      <c r="H198" s="111"/>
-      <c r="I198" s="111"/>
-      <c r="J198" s="111"/>
-      <c r="K198" s="111"/>
-      <c r="L198" s="111"/>
-      <c r="M198" s="111"/>
-      <c r="N198" s="111"/>
-      <c r="O198" s="111"/>
-      <c r="P198" s="111"/>
-      <c r="Q198" s="111"/>
-      <c r="R198" s="111"/>
-      <c r="S198" s="111"/>
-      <c r="T198" s="111"/>
+      <c r="F198" s="113"/>
+      <c r="G198" s="113"/>
+      <c r="H198" s="113"/>
+      <c r="I198" s="113"/>
+      <c r="J198" s="113"/>
+      <c r="K198" s="113"/>
+      <c r="L198" s="113"/>
+      <c r="M198" s="113"/>
+      <c r="N198" s="113"/>
+      <c r="O198" s="113"/>
+      <c r="P198" s="113"/>
+      <c r="Q198" s="113"/>
+      <c r="R198" s="113"/>
+      <c r="S198" s="113"/>
+      <c r="T198" s="113"/>
     </row>
     <row r="199" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E199" s="110" t="s">
+      <c r="E199" s="114" t="s">
         <v>318</v>
       </c>
-      <c r="F199" s="111"/>
-      <c r="G199" s="111"/>
-      <c r="H199" s="111"/>
-      <c r="I199" s="111"/>
-      <c r="J199" s="111"/>
-      <c r="K199" s="111"/>
-      <c r="L199" s="111"/>
-      <c r="M199" s="111"/>
-      <c r="N199" s="111"/>
-      <c r="O199" s="111"/>
-      <c r="P199" s="111"/>
-      <c r="Q199" s="111"/>
-      <c r="R199" s="111"/>
-      <c r="S199" s="111"/>
-      <c r="T199" s="111"/>
+      <c r="F199" s="113"/>
+      <c r="G199" s="113"/>
+      <c r="H199" s="113"/>
+      <c r="I199" s="113"/>
+      <c r="J199" s="113"/>
+      <c r="K199" s="113"/>
+      <c r="L199" s="113"/>
+      <c r="M199" s="113"/>
+      <c r="N199" s="113"/>
+      <c r="O199" s="113"/>
+      <c r="P199" s="113"/>
+      <c r="Q199" s="113"/>
+      <c r="R199" s="113"/>
+      <c r="S199" s="113"/>
+      <c r="T199" s="113"/>
     </row>
     <row r="200" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E200" s="110" t="s">
+      <c r="E200" s="114" t="s">
         <v>293</v>
       </c>
-      <c r="F200" s="111"/>
-      <c r="G200" s="111"/>
-      <c r="H200" s="111"/>
-      <c r="I200" s="111"/>
-      <c r="J200" s="111"/>
-      <c r="K200" s="111"/>
-      <c r="L200" s="111"/>
-      <c r="M200" s="111"/>
-      <c r="N200" s="111"/>
-      <c r="O200" s="111"/>
-      <c r="P200" s="111"/>
-      <c r="Q200" s="111"/>
-      <c r="R200" s="111"/>
-      <c r="S200" s="111"/>
-      <c r="T200" s="111"/>
+      <c r="F200" s="113"/>
+      <c r="G200" s="113"/>
+      <c r="H200" s="113"/>
+      <c r="I200" s="113"/>
+      <c r="J200" s="113"/>
+      <c r="K200" s="113"/>
+      <c r="L200" s="113"/>
+      <c r="M200" s="113"/>
+      <c r="N200" s="113"/>
+      <c r="O200" s="113"/>
+      <c r="P200" s="113"/>
+      <c r="Q200" s="113"/>
+      <c r="R200" s="113"/>
+      <c r="S200" s="113"/>
+      <c r="T200" s="113"/>
     </row>
     <row r="201" spans="5:20" ht="21" x14ac:dyDescent="0.35">
       <c r="E201" s="63" t="s">
@@ -14131,44 +14131,44 @@
       </c>
     </row>
     <row r="225" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E225" s="107" t="s">
+      <c r="E225" s="108" t="s">
         <v>318</v>
       </c>
-      <c r="F225" s="112"/>
-      <c r="G225" s="112"/>
-      <c r="H225" s="112"/>
-      <c r="I225" s="112"/>
-      <c r="J225" s="112"/>
-      <c r="K225" s="112"/>
-      <c r="L225" s="112"/>
-      <c r="M225" s="112"/>
-      <c r="N225" s="112"/>
-      <c r="O225" s="112"/>
-      <c r="P225" s="112"/>
-      <c r="Q225" s="112"/>
-      <c r="R225" s="112"/>
-      <c r="S225" s="112"/>
-      <c r="T225" s="113"/>
+      <c r="F225" s="109"/>
+      <c r="G225" s="109"/>
+      <c r="H225" s="109"/>
+      <c r="I225" s="109"/>
+      <c r="J225" s="109"/>
+      <c r="K225" s="109"/>
+      <c r="L225" s="109"/>
+      <c r="M225" s="109"/>
+      <c r="N225" s="109"/>
+      <c r="O225" s="109"/>
+      <c r="P225" s="109"/>
+      <c r="Q225" s="109"/>
+      <c r="R225" s="109"/>
+      <c r="S225" s="109"/>
+      <c r="T225" s="110"/>
     </row>
     <row r="226" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E226" s="112" t="s">
+      <c r="E226" s="109" t="s">
         <v>294</v>
       </c>
-      <c r="F226" s="108"/>
-      <c r="G226" s="108"/>
-      <c r="H226" s="108"/>
-      <c r="I226" s="108"/>
-      <c r="J226" s="108"/>
-      <c r="K226" s="108"/>
-      <c r="L226" s="108"/>
-      <c r="M226" s="108"/>
-      <c r="N226" s="108"/>
-      <c r="O226" s="108"/>
-      <c r="P226" s="108"/>
-      <c r="Q226" s="108"/>
-      <c r="R226" s="108"/>
-      <c r="S226" s="108"/>
-      <c r="T226" s="109"/>
+      <c r="F226" s="111"/>
+      <c r="G226" s="111"/>
+      <c r="H226" s="111"/>
+      <c r="I226" s="111"/>
+      <c r="J226" s="111"/>
+      <c r="K226" s="111"/>
+      <c r="L226" s="111"/>
+      <c r="M226" s="111"/>
+      <c r="N226" s="111"/>
+      <c r="O226" s="111"/>
+      <c r="P226" s="111"/>
+      <c r="Q226" s="111"/>
+      <c r="R226" s="111"/>
+      <c r="S226" s="111"/>
+      <c r="T226" s="112"/>
     </row>
     <row r="227" spans="5:20" ht="21" x14ac:dyDescent="0.25">
       <c r="E227" s="63" t="s">
@@ -14839,44 +14839,44 @@
       </c>
     </row>
     <row r="241" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E241" s="107" t="s">
+      <c r="E241" s="108" t="s">
         <v>319</v>
       </c>
-      <c r="F241" s="108"/>
-      <c r="G241" s="108"/>
-      <c r="H241" s="108"/>
-      <c r="I241" s="108"/>
-      <c r="J241" s="108"/>
-      <c r="K241" s="108"/>
-      <c r="L241" s="108"/>
-      <c r="M241" s="108"/>
-      <c r="N241" s="108"/>
-      <c r="O241" s="108"/>
-      <c r="P241" s="108"/>
-      <c r="Q241" s="108"/>
-      <c r="R241" s="108"/>
-      <c r="S241" s="108"/>
-      <c r="T241" s="109"/>
+      <c r="F241" s="111"/>
+      <c r="G241" s="111"/>
+      <c r="H241" s="111"/>
+      <c r="I241" s="111"/>
+      <c r="J241" s="111"/>
+      <c r="K241" s="111"/>
+      <c r="L241" s="111"/>
+      <c r="M241" s="111"/>
+      <c r="N241" s="111"/>
+      <c r="O241" s="111"/>
+      <c r="P241" s="111"/>
+      <c r="Q241" s="111"/>
+      <c r="R241" s="111"/>
+      <c r="S241" s="111"/>
+      <c r="T241" s="112"/>
     </row>
     <row r="242" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E242" s="107" t="s">
+      <c r="E242" s="108" t="s">
         <v>295</v>
       </c>
-      <c r="F242" s="108"/>
-      <c r="G242" s="108"/>
-      <c r="H242" s="108"/>
-      <c r="I242" s="108"/>
-      <c r="J242" s="108"/>
-      <c r="K242" s="108"/>
-      <c r="L242" s="108"/>
-      <c r="M242" s="108"/>
-      <c r="N242" s="108"/>
-      <c r="O242" s="108"/>
-      <c r="P242" s="108"/>
-      <c r="Q242" s="108"/>
-      <c r="R242" s="108"/>
-      <c r="S242" s="108"/>
-      <c r="T242" s="109"/>
+      <c r="F242" s="111"/>
+      <c r="G242" s="111"/>
+      <c r="H242" s="111"/>
+      <c r="I242" s="111"/>
+      <c r="J242" s="111"/>
+      <c r="K242" s="111"/>
+      <c r="L242" s="111"/>
+      <c r="M242" s="111"/>
+      <c r="N242" s="111"/>
+      <c r="O242" s="111"/>
+      <c r="P242" s="111"/>
+      <c r="Q242" s="111"/>
+      <c r="R242" s="111"/>
+      <c r="S242" s="111"/>
+      <c r="T242" s="112"/>
     </row>
     <row r="243" spans="5:20" ht="21" x14ac:dyDescent="0.25">
       <c r="E243" s="63" t="s">
@@ -15699,104 +15699,104 @@
       </c>
     </row>
     <row r="262" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E262" s="111" t="s">
+      <c r="E262" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="F262" s="111"/>
-      <c r="G262" s="111"/>
-      <c r="H262" s="111"/>
-      <c r="I262" s="111"/>
-      <c r="J262" s="111"/>
-      <c r="K262" s="111"/>
-      <c r="L262" s="111"/>
-      <c r="M262" s="111"/>
-      <c r="N262" s="111"/>
-      <c r="O262" s="111"/>
-      <c r="P262" s="111"/>
-      <c r="Q262" s="111"/>
-      <c r="R262" s="111"/>
-      <c r="S262" s="111"/>
-      <c r="T262" s="111"/>
+      <c r="F262" s="113"/>
+      <c r="G262" s="113"/>
+      <c r="H262" s="113"/>
+      <c r="I262" s="113"/>
+      <c r="J262" s="113"/>
+      <c r="K262" s="113"/>
+      <c r="L262" s="113"/>
+      <c r="M262" s="113"/>
+      <c r="N262" s="113"/>
+      <c r="O262" s="113"/>
+      <c r="P262" s="113"/>
+      <c r="Q262" s="113"/>
+      <c r="R262" s="113"/>
+      <c r="S262" s="113"/>
+      <c r="T262" s="113"/>
     </row>
     <row r="263" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E263" s="110" t="s">
+      <c r="E263" s="114" t="s">
         <v>291</v>
       </c>
-      <c r="F263" s="111"/>
-      <c r="G263" s="111"/>
-      <c r="H263" s="111"/>
-      <c r="I263" s="111"/>
-      <c r="J263" s="111"/>
-      <c r="K263" s="111"/>
-      <c r="L263" s="111"/>
-      <c r="M263" s="111"/>
-      <c r="N263" s="111"/>
-      <c r="O263" s="111"/>
-      <c r="P263" s="111"/>
-      <c r="Q263" s="111"/>
-      <c r="R263" s="111"/>
-      <c r="S263" s="111"/>
-      <c r="T263" s="111"/>
+      <c r="F263" s="113"/>
+      <c r="G263" s="113"/>
+      <c r="H263" s="113"/>
+      <c r="I263" s="113"/>
+      <c r="J263" s="113"/>
+      <c r="K263" s="113"/>
+      <c r="L263" s="113"/>
+      <c r="M263" s="113"/>
+      <c r="N263" s="113"/>
+      <c r="O263" s="113"/>
+      <c r="P263" s="113"/>
+      <c r="Q263" s="113"/>
+      <c r="R263" s="113"/>
+      <c r="S263" s="113"/>
+      <c r="T263" s="113"/>
     </row>
     <row r="264" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E264" s="110" t="s">
+      <c r="E264" s="114" t="s">
         <v>292</v>
       </c>
-      <c r="F264" s="111"/>
-      <c r="G264" s="111"/>
-      <c r="H264" s="111"/>
-      <c r="I264" s="111"/>
-      <c r="J264" s="111"/>
-      <c r="K264" s="111"/>
-      <c r="L264" s="111"/>
-      <c r="M264" s="111"/>
-      <c r="N264" s="111"/>
-      <c r="O264" s="111"/>
-      <c r="P264" s="111"/>
-      <c r="Q264" s="111"/>
-      <c r="R264" s="111"/>
-      <c r="S264" s="111"/>
-      <c r="T264" s="111"/>
+      <c r="F264" s="113"/>
+      <c r="G264" s="113"/>
+      <c r="H264" s="113"/>
+      <c r="I264" s="113"/>
+      <c r="J264" s="113"/>
+      <c r="K264" s="113"/>
+      <c r="L264" s="113"/>
+      <c r="M264" s="113"/>
+      <c r="N264" s="113"/>
+      <c r="O264" s="113"/>
+      <c r="P264" s="113"/>
+      <c r="Q264" s="113"/>
+      <c r="R264" s="113"/>
+      <c r="S264" s="113"/>
+      <c r="T264" s="113"/>
     </row>
     <row r="265" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E265" s="110" t="s">
+      <c r="E265" s="114" t="s">
         <v>314</v>
       </c>
-      <c r="F265" s="111"/>
-      <c r="G265" s="111"/>
-      <c r="H265" s="111"/>
-      <c r="I265" s="111"/>
-      <c r="J265" s="111"/>
-      <c r="K265" s="111"/>
-      <c r="L265" s="111"/>
-      <c r="M265" s="111"/>
-      <c r="N265" s="111"/>
-      <c r="O265" s="111"/>
-      <c r="P265" s="111"/>
-      <c r="Q265" s="111"/>
-      <c r="R265" s="111"/>
-      <c r="S265" s="111"/>
-      <c r="T265" s="111"/>
+      <c r="F265" s="113"/>
+      <c r="G265" s="113"/>
+      <c r="H265" s="113"/>
+      <c r="I265" s="113"/>
+      <c r="J265" s="113"/>
+      <c r="K265" s="113"/>
+      <c r="L265" s="113"/>
+      <c r="M265" s="113"/>
+      <c r="N265" s="113"/>
+      <c r="O265" s="113"/>
+      <c r="P265" s="113"/>
+      <c r="Q265" s="113"/>
+      <c r="R265" s="113"/>
+      <c r="S265" s="113"/>
+      <c r="T265" s="113"/>
     </row>
     <row r="266" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E266" s="110" t="s">
+      <c r="E266" s="114" t="s">
         <v>293</v>
       </c>
-      <c r="F266" s="111"/>
-      <c r="G266" s="111"/>
-      <c r="H266" s="111"/>
-      <c r="I266" s="111"/>
-      <c r="J266" s="111"/>
-      <c r="K266" s="111"/>
-      <c r="L266" s="111"/>
-      <c r="M266" s="111"/>
-      <c r="N266" s="111"/>
-      <c r="O266" s="111"/>
-      <c r="P266" s="111"/>
-      <c r="Q266" s="111"/>
-      <c r="R266" s="111"/>
-      <c r="S266" s="111"/>
-      <c r="T266" s="111"/>
+      <c r="F266" s="113"/>
+      <c r="G266" s="113"/>
+      <c r="H266" s="113"/>
+      <c r="I266" s="113"/>
+      <c r="J266" s="113"/>
+      <c r="K266" s="113"/>
+      <c r="L266" s="113"/>
+      <c r="M266" s="113"/>
+      <c r="N266" s="113"/>
+      <c r="O266" s="113"/>
+      <c r="P266" s="113"/>
+      <c r="Q266" s="113"/>
+      <c r="R266" s="113"/>
+      <c r="S266" s="113"/>
+      <c r="T266" s="113"/>
     </row>
     <row r="267" spans="5:20" ht="21" x14ac:dyDescent="0.35">
       <c r="E267" s="63" t="s">
@@ -16967,44 +16967,44 @@
       </c>
     </row>
     <row r="291" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E291" s="107" t="s">
+      <c r="E291" s="108" t="s">
         <v>314</v>
       </c>
-      <c r="F291" s="112"/>
-      <c r="G291" s="112"/>
-      <c r="H291" s="112"/>
-      <c r="I291" s="112"/>
-      <c r="J291" s="112"/>
-      <c r="K291" s="112"/>
-      <c r="L291" s="112"/>
-      <c r="M291" s="112"/>
-      <c r="N291" s="112"/>
-      <c r="O291" s="112"/>
-      <c r="P291" s="112"/>
-      <c r="Q291" s="112"/>
-      <c r="R291" s="112"/>
-      <c r="S291" s="112"/>
-      <c r="T291" s="113"/>
+      <c r="F291" s="109"/>
+      <c r="G291" s="109"/>
+      <c r="H291" s="109"/>
+      <c r="I291" s="109"/>
+      <c r="J291" s="109"/>
+      <c r="K291" s="109"/>
+      <c r="L291" s="109"/>
+      <c r="M291" s="109"/>
+      <c r="N291" s="109"/>
+      <c r="O291" s="109"/>
+      <c r="P291" s="109"/>
+      <c r="Q291" s="109"/>
+      <c r="R291" s="109"/>
+      <c r="S291" s="109"/>
+      <c r="T291" s="110"/>
     </row>
     <row r="292" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E292" s="112" t="s">
+      <c r="E292" s="109" t="s">
         <v>294</v>
       </c>
-      <c r="F292" s="108"/>
-      <c r="G292" s="108"/>
-      <c r="H292" s="108"/>
-      <c r="I292" s="108"/>
-      <c r="J292" s="108"/>
-      <c r="K292" s="108"/>
-      <c r="L292" s="108"/>
-      <c r="M292" s="108"/>
-      <c r="N292" s="108"/>
-      <c r="O292" s="108"/>
-      <c r="P292" s="108"/>
-      <c r="Q292" s="108"/>
-      <c r="R292" s="108"/>
-      <c r="S292" s="108"/>
-      <c r="T292" s="109"/>
+      <c r="F292" s="111"/>
+      <c r="G292" s="111"/>
+      <c r="H292" s="111"/>
+      <c r="I292" s="111"/>
+      <c r="J292" s="111"/>
+      <c r="K292" s="111"/>
+      <c r="L292" s="111"/>
+      <c r="M292" s="111"/>
+      <c r="N292" s="111"/>
+      <c r="O292" s="111"/>
+      <c r="P292" s="111"/>
+      <c r="Q292" s="111"/>
+      <c r="R292" s="111"/>
+      <c r="S292" s="111"/>
+      <c r="T292" s="112"/>
     </row>
     <row r="293" spans="5:20" ht="21" x14ac:dyDescent="0.25">
       <c r="E293" s="63" t="s">
@@ -17675,44 +17675,44 @@
       </c>
     </row>
     <row r="307" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E307" s="107" t="s">
+      <c r="E307" s="108" t="s">
         <v>315</v>
       </c>
-      <c r="F307" s="108"/>
-      <c r="G307" s="108"/>
-      <c r="H307" s="108"/>
-      <c r="I307" s="108"/>
-      <c r="J307" s="108"/>
-      <c r="K307" s="108"/>
-      <c r="L307" s="108"/>
-      <c r="M307" s="108"/>
-      <c r="N307" s="108"/>
-      <c r="O307" s="108"/>
-      <c r="P307" s="108"/>
-      <c r="Q307" s="108"/>
-      <c r="R307" s="108"/>
-      <c r="S307" s="108"/>
-      <c r="T307" s="109"/>
+      <c r="F307" s="111"/>
+      <c r="G307" s="111"/>
+      <c r="H307" s="111"/>
+      <c r="I307" s="111"/>
+      <c r="J307" s="111"/>
+      <c r="K307" s="111"/>
+      <c r="L307" s="111"/>
+      <c r="M307" s="111"/>
+      <c r="N307" s="111"/>
+      <c r="O307" s="111"/>
+      <c r="P307" s="111"/>
+      <c r="Q307" s="111"/>
+      <c r="R307" s="111"/>
+      <c r="S307" s="111"/>
+      <c r="T307" s="112"/>
     </row>
     <row r="308" spans="5:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="E308" s="107" t="s">
+      <c r="E308" s="108" t="s">
         <v>295</v>
       </c>
-      <c r="F308" s="108"/>
-      <c r="G308" s="108"/>
-      <c r="H308" s="108"/>
-      <c r="I308" s="108"/>
-      <c r="J308" s="108"/>
-      <c r="K308" s="108"/>
-      <c r="L308" s="108"/>
-      <c r="M308" s="108"/>
-      <c r="N308" s="108"/>
-      <c r="O308" s="108"/>
-      <c r="P308" s="108"/>
-      <c r="Q308" s="108"/>
-      <c r="R308" s="108"/>
-      <c r="S308" s="108"/>
-      <c r="T308" s="109"/>
+      <c r="F308" s="111"/>
+      <c r="G308" s="111"/>
+      <c r="H308" s="111"/>
+      <c r="I308" s="111"/>
+      <c r="J308" s="111"/>
+      <c r="K308" s="111"/>
+      <c r="L308" s="111"/>
+      <c r="M308" s="111"/>
+      <c r="N308" s="111"/>
+      <c r="O308" s="111"/>
+      <c r="P308" s="111"/>
+      <c r="Q308" s="111"/>
+      <c r="R308" s="111"/>
+      <c r="S308" s="111"/>
+      <c r="T308" s="112"/>
     </row>
     <row r="309" spans="5:20" ht="21" x14ac:dyDescent="0.25">
       <c r="E309" s="63" t="s">
@@ -18539,6 +18539,42 @@
     <sortCondition descending="1" ref="I73"/>
   </sortState>
   <mergeCells count="45">
+    <mergeCell ref="E308:T308"/>
+    <mergeCell ref="E265:T265"/>
+    <mergeCell ref="E266:T266"/>
+    <mergeCell ref="E291:T291"/>
+    <mergeCell ref="E292:T292"/>
+    <mergeCell ref="E307:T307"/>
+    <mergeCell ref="E241:T241"/>
+    <mergeCell ref="E242:T242"/>
+    <mergeCell ref="E262:T262"/>
+    <mergeCell ref="E263:T263"/>
+    <mergeCell ref="E264:T264"/>
+    <mergeCell ref="E198:T198"/>
+    <mergeCell ref="E199:T199"/>
+    <mergeCell ref="E200:T200"/>
+    <mergeCell ref="E225:T225"/>
+    <mergeCell ref="E226:T226"/>
+    <mergeCell ref="E161:T161"/>
+    <mergeCell ref="E176:T176"/>
+    <mergeCell ref="E177:T177"/>
+    <mergeCell ref="E196:T196"/>
+    <mergeCell ref="E197:T197"/>
+    <mergeCell ref="E132:T132"/>
+    <mergeCell ref="E133:T133"/>
+    <mergeCell ref="E134:T134"/>
+    <mergeCell ref="E135:T135"/>
+    <mergeCell ref="E160:T160"/>
+    <mergeCell ref="E95:T95"/>
+    <mergeCell ref="E96:T96"/>
+    <mergeCell ref="E111:T111"/>
+    <mergeCell ref="E112:T112"/>
+    <mergeCell ref="E131:T131"/>
+    <mergeCell ref="E66:T66"/>
+    <mergeCell ref="E67:T67"/>
+    <mergeCell ref="E68:T68"/>
+    <mergeCell ref="E69:T69"/>
+    <mergeCell ref="E70:T70"/>
     <mergeCell ref="E30:T30"/>
     <mergeCell ref="E31:T31"/>
     <mergeCell ref="E46:T46"/>
@@ -18548,42 +18584,6 @@
     <mergeCell ref="E3:T3"/>
     <mergeCell ref="E4:T4"/>
     <mergeCell ref="E5:T5"/>
-    <mergeCell ref="E66:T66"/>
-    <mergeCell ref="E67:T67"/>
-    <mergeCell ref="E68:T68"/>
-    <mergeCell ref="E69:T69"/>
-    <mergeCell ref="E70:T70"/>
-    <mergeCell ref="E95:T95"/>
-    <mergeCell ref="E96:T96"/>
-    <mergeCell ref="E111:T111"/>
-    <mergeCell ref="E112:T112"/>
-    <mergeCell ref="E131:T131"/>
-    <mergeCell ref="E132:T132"/>
-    <mergeCell ref="E133:T133"/>
-    <mergeCell ref="E134:T134"/>
-    <mergeCell ref="E135:T135"/>
-    <mergeCell ref="E160:T160"/>
-    <mergeCell ref="E161:T161"/>
-    <mergeCell ref="E176:T176"/>
-    <mergeCell ref="E177:T177"/>
-    <mergeCell ref="E196:T196"/>
-    <mergeCell ref="E197:T197"/>
-    <mergeCell ref="E198:T198"/>
-    <mergeCell ref="E199:T199"/>
-    <mergeCell ref="E200:T200"/>
-    <mergeCell ref="E225:T225"/>
-    <mergeCell ref="E226:T226"/>
-    <mergeCell ref="E241:T241"/>
-    <mergeCell ref="E242:T242"/>
-    <mergeCell ref="E262:T262"/>
-    <mergeCell ref="E263:T263"/>
-    <mergeCell ref="E264:T264"/>
-    <mergeCell ref="E308:T308"/>
-    <mergeCell ref="E265:T265"/>
-    <mergeCell ref="E266:T266"/>
-    <mergeCell ref="E291:T291"/>
-    <mergeCell ref="E292:T292"/>
-    <mergeCell ref="E307:T307"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18602,20 +18602,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="152" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
     </row>
     <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
@@ -18819,20 +18819,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="152" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
     </row>
     <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
@@ -19035,18 +19035,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="152" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
@@ -19149,69 +19149,69 @@
   </cols>
   <sheetData>
     <row r="7" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F7" s="152" t="s">
+      <c r="F7" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="152"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="153"/>
+      <c r="L7" s="153"/>
+      <c r="M7" s="153"/>
+      <c r="N7" s="153"/>
     </row>
     <row r="8" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F8" s="153" t="s">
+      <c r="F8" s="154" t="s">
         <v>320</v>
       </c>
-      <c r="G8" s="152"/>
-      <c r="H8" s="152"/>
-      <c r="I8" s="152"/>
-      <c r="J8" s="152"/>
-      <c r="K8" s="152"/>
-      <c r="L8" s="152"/>
-      <c r="M8" s="152"/>
-      <c r="N8" s="152"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
+      <c r="I8" s="153"/>
+      <c r="J8" s="153"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="153"/>
+      <c r="M8" s="153"/>
+      <c r="N8" s="153"/>
     </row>
     <row r="9" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F9" s="153" t="s">
+      <c r="F9" s="154" t="s">
         <v>321</v>
       </c>
-      <c r="G9" s="152"/>
-      <c r="H9" s="152"/>
-      <c r="I9" s="152"/>
-      <c r="J9" s="152"/>
-      <c r="K9" s="152"/>
-      <c r="L9" s="152"/>
-      <c r="M9" s="152"/>
-      <c r="N9" s="152"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="153"/>
+      <c r="I9" s="153"/>
+      <c r="J9" s="153"/>
+      <c r="K9" s="153"/>
+      <c r="L9" s="153"/>
+      <c r="M9" s="153"/>
+      <c r="N9" s="153"/>
     </row>
     <row r="10" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F10" s="153" t="s">
+      <c r="F10" s="154" t="s">
         <v>325</v>
       </c>
-      <c r="G10" s="152"/>
-      <c r="H10" s="152"/>
-      <c r="I10" s="152"/>
-      <c r="J10" s="152"/>
-      <c r="K10" s="152"/>
-      <c r="L10" s="152"/>
-      <c r="M10" s="152"/>
-      <c r="N10" s="152"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="153"/>
+      <c r="K10" s="153"/>
+      <c r="L10" s="153"/>
+      <c r="M10" s="153"/>
+      <c r="N10" s="153"/>
     </row>
     <row r="11" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F11" s="153" t="s">
+      <c r="F11" s="154" t="s">
         <v>598</v>
       </c>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="152"/>
-      <c r="K11" s="152"/>
-      <c r="L11" s="152"/>
-      <c r="M11" s="152"/>
-      <c r="N11" s="152"/>
+      <c r="G11" s="153"/>
+      <c r="H11" s="153"/>
+      <c r="I11" s="153"/>
+      <c r="J11" s="153"/>
+      <c r="K11" s="153"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="153"/>
+      <c r="N11" s="153"/>
     </row>
     <row r="12" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="F12" s="72" t="s">
@@ -19960,69 +19960,69 @@
       <c r="N50" s="89"/>
     </row>
     <row r="51" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F51" s="152" t="s">
+      <c r="F51" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="G51" s="152"/>
-      <c r="H51" s="152"/>
-      <c r="I51" s="152"/>
-      <c r="J51" s="152"/>
-      <c r="K51" s="152"/>
-      <c r="L51" s="152"/>
-      <c r="M51" s="152"/>
-      <c r="N51" s="152"/>
+      <c r="G51" s="153"/>
+      <c r="H51" s="153"/>
+      <c r="I51" s="153"/>
+      <c r="J51" s="153"/>
+      <c r="K51" s="153"/>
+      <c r="L51" s="153"/>
+      <c r="M51" s="153"/>
+      <c r="N51" s="153"/>
     </row>
     <row r="52" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F52" s="153" t="s">
+      <c r="F52" s="154" t="s">
         <v>320</v>
       </c>
-      <c r="G52" s="152"/>
-      <c r="H52" s="152"/>
-      <c r="I52" s="152"/>
-      <c r="J52" s="152"/>
-      <c r="K52" s="152"/>
-      <c r="L52" s="152"/>
-      <c r="M52" s="152"/>
-      <c r="N52" s="152"/>
+      <c r="G52" s="153"/>
+      <c r="H52" s="153"/>
+      <c r="I52" s="153"/>
+      <c r="J52" s="153"/>
+      <c r="K52" s="153"/>
+      <c r="L52" s="153"/>
+      <c r="M52" s="153"/>
+      <c r="N52" s="153"/>
     </row>
     <row r="53" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F53" s="153" t="s">
+      <c r="F53" s="154" t="s">
         <v>321</v>
       </c>
-      <c r="G53" s="152"/>
-      <c r="H53" s="152"/>
-      <c r="I53" s="152"/>
-      <c r="J53" s="152"/>
-      <c r="K53" s="152"/>
-      <c r="L53" s="152"/>
-      <c r="M53" s="152"/>
-      <c r="N53" s="152"/>
+      <c r="G53" s="153"/>
+      <c r="H53" s="153"/>
+      <c r="I53" s="153"/>
+      <c r="J53" s="153"/>
+      <c r="K53" s="153"/>
+      <c r="L53" s="153"/>
+      <c r="M53" s="153"/>
+      <c r="N53" s="153"/>
     </row>
     <row r="54" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F54" s="153" t="s">
+      <c r="F54" s="154" t="s">
         <v>325</v>
       </c>
-      <c r="G54" s="152"/>
-      <c r="H54" s="152"/>
-      <c r="I54" s="152"/>
-      <c r="J54" s="152"/>
-      <c r="K54" s="152"/>
-      <c r="L54" s="152"/>
-      <c r="M54" s="152"/>
-      <c r="N54" s="152"/>
+      <c r="G54" s="153"/>
+      <c r="H54" s="153"/>
+      <c r="I54" s="153"/>
+      <c r="J54" s="153"/>
+      <c r="K54" s="153"/>
+      <c r="L54" s="153"/>
+      <c r="M54" s="153"/>
+      <c r="N54" s="153"/>
     </row>
     <row r="55" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F55" s="153" t="s">
+      <c r="F55" s="154" t="s">
         <v>654</v>
       </c>
-      <c r="G55" s="152"/>
-      <c r="H55" s="152"/>
-      <c r="I55" s="152"/>
-      <c r="J55" s="152"/>
-      <c r="K55" s="152"/>
-      <c r="L55" s="152"/>
-      <c r="M55" s="152"/>
-      <c r="N55" s="152"/>
+      <c r="G55" s="153"/>
+      <c r="H55" s="153"/>
+      <c r="I55" s="153"/>
+      <c r="J55" s="153"/>
+      <c r="K55" s="153"/>
+      <c r="L55" s="153"/>
+      <c r="M55" s="153"/>
+      <c r="N55" s="153"/>
     </row>
     <row r="56" spans="6:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="F56" s="72" t="s">
@@ -20749,74 +20749,74 @@
       <c r="N92" s="75"/>
     </row>
     <row r="96" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D96" s="152" t="s">
+      <c r="D96" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="E96" s="152"/>
-      <c r="F96" s="152"/>
-      <c r="G96" s="152"/>
-      <c r="H96" s="152"/>
-      <c r="I96" s="152"/>
-      <c r="J96" s="152"/>
-      <c r="K96" s="152"/>
-      <c r="L96" s="152"/>
-      <c r="M96" s="152"/>
+      <c r="E96" s="153"/>
+      <c r="F96" s="153"/>
+      <c r="G96" s="153"/>
+      <c r="H96" s="153"/>
+      <c r="I96" s="153"/>
+      <c r="J96" s="153"/>
+      <c r="K96" s="153"/>
+      <c r="L96" s="153"/>
+      <c r="M96" s="153"/>
     </row>
     <row r="97" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D97" s="153" t="s">
+      <c r="D97" s="154" t="s">
         <v>320</v>
       </c>
-      <c r="E97" s="152"/>
-      <c r="F97" s="152"/>
-      <c r="G97" s="152"/>
-      <c r="H97" s="152"/>
-      <c r="I97" s="152"/>
-      <c r="J97" s="152"/>
-      <c r="K97" s="152"/>
-      <c r="L97" s="152"/>
-      <c r="M97" s="152"/>
+      <c r="E97" s="153"/>
+      <c r="F97" s="153"/>
+      <c r="G97" s="153"/>
+      <c r="H97" s="153"/>
+      <c r="I97" s="153"/>
+      <c r="J97" s="153"/>
+      <c r="K97" s="153"/>
+      <c r="L97" s="153"/>
+      <c r="M97" s="153"/>
     </row>
     <row r="98" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D98" s="153" t="s">
+      <c r="D98" s="154" t="s">
         <v>321</v>
       </c>
-      <c r="E98" s="152"/>
-      <c r="F98" s="152"/>
-      <c r="G98" s="152"/>
-      <c r="H98" s="152"/>
-      <c r="I98" s="152"/>
-      <c r="J98" s="152"/>
-      <c r="K98" s="152"/>
-      <c r="L98" s="152"/>
-      <c r="M98" s="152"/>
+      <c r="E98" s="153"/>
+      <c r="F98" s="153"/>
+      <c r="G98" s="153"/>
+      <c r="H98" s="153"/>
+      <c r="I98" s="153"/>
+      <c r="J98" s="153"/>
+      <c r="K98" s="153"/>
+      <c r="L98" s="153"/>
+      <c r="M98" s="153"/>
     </row>
     <row r="99" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D99" s="153" t="s">
+      <c r="D99" s="154" t="s">
         <v>325</v>
       </c>
-      <c r="E99" s="152"/>
-      <c r="F99" s="152"/>
-      <c r="G99" s="152"/>
-      <c r="H99" s="152"/>
-      <c r="I99" s="152"/>
-      <c r="J99" s="152"/>
-      <c r="K99" s="152"/>
-      <c r="L99" s="152"/>
-      <c r="M99" s="152"/>
+      <c r="E99" s="153"/>
+      <c r="F99" s="153"/>
+      <c r="G99" s="153"/>
+      <c r="H99" s="153"/>
+      <c r="I99" s="153"/>
+      <c r="J99" s="153"/>
+      <c r="K99" s="153"/>
+      <c r="L99" s="153"/>
+      <c r="M99" s="153"/>
     </row>
     <row r="100" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D100" s="153" t="s">
+      <c r="D100" s="154" t="s">
         <v>397</v>
       </c>
-      <c r="E100" s="152"/>
-      <c r="F100" s="152"/>
-      <c r="G100" s="152"/>
-      <c r="H100" s="152"/>
-      <c r="I100" s="152"/>
-      <c r="J100" s="152"/>
-      <c r="K100" s="152"/>
-      <c r="L100" s="152"/>
-      <c r="M100" s="152"/>
+      <c r="E100" s="153"/>
+      <c r="F100" s="153"/>
+      <c r="G100" s="153"/>
+      <c r="H100" s="153"/>
+      <c r="I100" s="153"/>
+      <c r="J100" s="153"/>
+      <c r="K100" s="153"/>
+      <c r="L100" s="153"/>
+      <c r="M100" s="153"/>
     </row>
     <row r="101" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D101" s="72" t="s">
@@ -22045,74 +22045,74 @@
       </c>
     </row>
     <row r="183" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D183" s="152" t="s">
+      <c r="D183" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="E183" s="152"/>
-      <c r="F183" s="152"/>
-      <c r="G183" s="152"/>
-      <c r="H183" s="152"/>
-      <c r="I183" s="152"/>
-      <c r="J183" s="152"/>
-      <c r="K183" s="152"/>
-      <c r="L183" s="152"/>
-      <c r="M183" s="152"/>
+      <c r="E183" s="153"/>
+      <c r="F183" s="153"/>
+      <c r="G183" s="153"/>
+      <c r="H183" s="153"/>
+      <c r="I183" s="153"/>
+      <c r="J183" s="153"/>
+      <c r="K183" s="153"/>
+      <c r="L183" s="153"/>
+      <c r="M183" s="153"/>
     </row>
     <row r="184" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D184" s="153" t="s">
+      <c r="D184" s="154" t="s">
         <v>320</v>
       </c>
-      <c r="E184" s="152"/>
-      <c r="F184" s="152"/>
-      <c r="G184" s="152"/>
-      <c r="H184" s="152"/>
-      <c r="I184" s="152"/>
-      <c r="J184" s="152"/>
-      <c r="K184" s="152"/>
-      <c r="L184" s="152"/>
-      <c r="M184" s="152"/>
+      <c r="E184" s="153"/>
+      <c r="F184" s="153"/>
+      <c r="G184" s="153"/>
+      <c r="H184" s="153"/>
+      <c r="I184" s="153"/>
+      <c r="J184" s="153"/>
+      <c r="K184" s="153"/>
+      <c r="L184" s="153"/>
+      <c r="M184" s="153"/>
     </row>
     <row r="185" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D185" s="153" t="s">
+      <c r="D185" s="154" t="s">
         <v>321</v>
       </c>
-      <c r="E185" s="152"/>
-      <c r="F185" s="152"/>
-      <c r="G185" s="152"/>
-      <c r="H185" s="152"/>
-      <c r="I185" s="152"/>
-      <c r="J185" s="152"/>
-      <c r="K185" s="152"/>
-      <c r="L185" s="152"/>
-      <c r="M185" s="152"/>
+      <c r="E185" s="153"/>
+      <c r="F185" s="153"/>
+      <c r="G185" s="153"/>
+      <c r="H185" s="153"/>
+      <c r="I185" s="153"/>
+      <c r="J185" s="153"/>
+      <c r="K185" s="153"/>
+      <c r="L185" s="153"/>
+      <c r="M185" s="153"/>
     </row>
     <row r="186" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D186" s="153" t="s">
+      <c r="D186" s="154" t="s">
         <v>325</v>
       </c>
-      <c r="E186" s="152"/>
-      <c r="F186" s="152"/>
-      <c r="G186" s="152"/>
-      <c r="H186" s="152"/>
-      <c r="I186" s="152"/>
-      <c r="J186" s="152"/>
-      <c r="K186" s="152"/>
-      <c r="L186" s="152"/>
-      <c r="M186" s="152"/>
+      <c r="E186" s="153"/>
+      <c r="F186" s="153"/>
+      <c r="G186" s="153"/>
+      <c r="H186" s="153"/>
+      <c r="I186" s="153"/>
+      <c r="J186" s="153"/>
+      <c r="K186" s="153"/>
+      <c r="L186" s="153"/>
+      <c r="M186" s="153"/>
     </row>
     <row r="187" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D187" s="153" t="s">
+      <c r="D187" s="154" t="s">
         <v>322</v>
       </c>
-      <c r="E187" s="152"/>
-      <c r="F187" s="152"/>
-      <c r="G187" s="152"/>
-      <c r="H187" s="152"/>
-      <c r="I187" s="152"/>
-      <c r="J187" s="152"/>
-      <c r="K187" s="152"/>
-      <c r="L187" s="152"/>
-      <c r="M187" s="152"/>
+      <c r="E187" s="153"/>
+      <c r="F187" s="153"/>
+      <c r="G187" s="153"/>
+      <c r="H187" s="153"/>
+      <c r="I187" s="153"/>
+      <c r="J187" s="153"/>
+      <c r="K187" s="153"/>
+      <c r="L187" s="153"/>
+      <c r="M187" s="153"/>
     </row>
     <row r="188" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D188" s="72" t="s">
@@ -22811,32 +22811,32 @@
       </c>
     </row>
     <row r="212" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D212" s="156" t="s">
+      <c r="D212" s="157" t="s">
         <v>332</v>
       </c>
-      <c r="E212" s="154"/>
-      <c r="F212" s="154"/>
-      <c r="G212" s="154"/>
-      <c r="H212" s="154"/>
-      <c r="I212" s="154"/>
-      <c r="J212" s="154"/>
-      <c r="K212" s="154"/>
-      <c r="L212" s="154"/>
-      <c r="M212" s="154"/>
+      <c r="E212" s="155"/>
+      <c r="F212" s="155"/>
+      <c r="G212" s="155"/>
+      <c r="H212" s="155"/>
+      <c r="I212" s="155"/>
+      <c r="J212" s="155"/>
+      <c r="K212" s="155"/>
+      <c r="L212" s="155"/>
+      <c r="M212" s="155"/>
     </row>
     <row r="213" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D213" s="154" t="s">
+      <c r="D213" s="155" t="s">
         <v>323</v>
       </c>
-      <c r="E213" s="155"/>
-      <c r="F213" s="155"/>
-      <c r="G213" s="155"/>
-      <c r="H213" s="155"/>
-      <c r="I213" s="155"/>
-      <c r="J213" s="155"/>
-      <c r="K213" s="155"/>
-      <c r="L213" s="155"/>
-      <c r="M213" s="155"/>
+      <c r="E213" s="156"/>
+      <c r="F213" s="156"/>
+      <c r="G213" s="156"/>
+      <c r="H213" s="156"/>
+      <c r="I213" s="156"/>
+      <c r="J213" s="156"/>
+      <c r="K213" s="156"/>
+      <c r="L213" s="156"/>
+      <c r="M213" s="156"/>
     </row>
     <row r="214" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D214" s="72" t="s">
@@ -23151,32 +23151,32 @@
       <c r="M227" s="75"/>
     </row>
     <row r="228" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D228" s="156" t="s">
+      <c r="D228" s="157" t="s">
         <v>332</v>
       </c>
-      <c r="E228" s="155"/>
-      <c r="F228" s="155"/>
-      <c r="G228" s="155"/>
-      <c r="H228" s="155"/>
-      <c r="I228" s="155"/>
-      <c r="J228" s="155"/>
-      <c r="K228" s="155"/>
-      <c r="L228" s="155"/>
-      <c r="M228" s="155"/>
+      <c r="E228" s="156"/>
+      <c r="F228" s="156"/>
+      <c r="G228" s="156"/>
+      <c r="H228" s="156"/>
+      <c r="I228" s="156"/>
+      <c r="J228" s="156"/>
+      <c r="K228" s="156"/>
+      <c r="L228" s="156"/>
+      <c r="M228" s="156"/>
     </row>
     <row r="229" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D229" s="156" t="s">
+      <c r="D229" s="157" t="s">
         <v>324</v>
       </c>
-      <c r="E229" s="155"/>
-      <c r="F229" s="155"/>
-      <c r="G229" s="155"/>
-      <c r="H229" s="155"/>
-      <c r="I229" s="155"/>
-      <c r="J229" s="155"/>
-      <c r="K229" s="155"/>
-      <c r="L229" s="155"/>
-      <c r="M229" s="155"/>
+      <c r="E229" s="156"/>
+      <c r="F229" s="156"/>
+      <c r="G229" s="156"/>
+      <c r="H229" s="156"/>
+      <c r="I229" s="156"/>
+      <c r="J229" s="156"/>
+      <c r="K229" s="156"/>
+      <c r="L229" s="156"/>
+      <c r="M229" s="156"/>
     </row>
     <row r="230" spans="4:13" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D230" s="72" t="s">
@@ -23925,16 +23925,11 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="F7:N7"/>
-    <mergeCell ref="F8:N8"/>
-    <mergeCell ref="F9:N9"/>
-    <mergeCell ref="F10:N10"/>
-    <mergeCell ref="F11:N11"/>
-    <mergeCell ref="D96:M96"/>
-    <mergeCell ref="D97:M97"/>
-    <mergeCell ref="D98:M98"/>
-    <mergeCell ref="D99:M99"/>
-    <mergeCell ref="D100:M100"/>
+    <mergeCell ref="F51:N51"/>
+    <mergeCell ref="F52:N52"/>
+    <mergeCell ref="F53:N53"/>
+    <mergeCell ref="F54:N54"/>
+    <mergeCell ref="F55:N55"/>
     <mergeCell ref="D213:M213"/>
     <mergeCell ref="D228:M228"/>
     <mergeCell ref="D229:M229"/>
@@ -23944,11 +23939,16 @@
     <mergeCell ref="D186:M186"/>
     <mergeCell ref="D187:M187"/>
     <mergeCell ref="D212:M212"/>
-    <mergeCell ref="F51:N51"/>
-    <mergeCell ref="F52:N52"/>
-    <mergeCell ref="F53:N53"/>
-    <mergeCell ref="F54:N54"/>
-    <mergeCell ref="F55:N55"/>
+    <mergeCell ref="D96:M96"/>
+    <mergeCell ref="D97:M97"/>
+    <mergeCell ref="D98:M98"/>
+    <mergeCell ref="D99:M99"/>
+    <mergeCell ref="D100:M100"/>
+    <mergeCell ref="F7:N7"/>
+    <mergeCell ref="F8:N8"/>
+    <mergeCell ref="F9:N9"/>
+    <mergeCell ref="F10:N10"/>
+    <mergeCell ref="F11:N11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -24081,74 +24081,74 @@
   </cols>
   <sheetData>
     <row r="7" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F7" s="152" t="s">
+      <c r="F7" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="152"/>
-      <c r="O7" s="152"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="153"/>
+      <c r="L7" s="153"/>
+      <c r="M7" s="153"/>
+      <c r="N7" s="153"/>
+      <c r="O7" s="153"/>
     </row>
     <row r="8" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F8" s="153" t="s">
+      <c r="F8" s="154" t="s">
         <v>320</v>
       </c>
-      <c r="G8" s="152"/>
-      <c r="H8" s="152"/>
-      <c r="I8" s="152"/>
-      <c r="J8" s="152"/>
-      <c r="K8" s="152"/>
-      <c r="L8" s="152"/>
-      <c r="M8" s="152"/>
-      <c r="N8" s="152"/>
-      <c r="O8" s="152"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
+      <c r="I8" s="153"/>
+      <c r="J8" s="153"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="153"/>
+      <c r="M8" s="153"/>
+      <c r="N8" s="153"/>
+      <c r="O8" s="153"/>
     </row>
     <row r="9" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F9" s="153" t="s">
+      <c r="F9" s="154" t="s">
         <v>321</v>
       </c>
-      <c r="G9" s="152"/>
-      <c r="H9" s="152"/>
-      <c r="I9" s="152"/>
-      <c r="J9" s="152"/>
-      <c r="K9" s="152"/>
-      <c r="L9" s="152"/>
-      <c r="M9" s="152"/>
-      <c r="N9" s="152"/>
-      <c r="O9" s="152"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="153"/>
+      <c r="I9" s="153"/>
+      <c r="J9" s="153"/>
+      <c r="K9" s="153"/>
+      <c r="L9" s="153"/>
+      <c r="M9" s="153"/>
+      <c r="N9" s="153"/>
+      <c r="O9" s="153"/>
     </row>
     <row r="10" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F10" s="153" t="s">
+      <c r="F10" s="154" t="s">
         <v>655</v>
       </c>
-      <c r="G10" s="152"/>
-      <c r="H10" s="152"/>
-      <c r="I10" s="152"/>
-      <c r="J10" s="152"/>
-      <c r="K10" s="152"/>
-      <c r="L10" s="152"/>
-      <c r="M10" s="152"/>
-      <c r="N10" s="152"/>
-      <c r="O10" s="152"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="153"/>
+      <c r="K10" s="153"/>
+      <c r="L10" s="153"/>
+      <c r="M10" s="153"/>
+      <c r="N10" s="153"/>
+      <c r="O10" s="153"/>
     </row>
     <row r="11" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F11" s="153" t="s">
+      <c r="F11" s="154" t="s">
         <v>598</v>
       </c>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="152"/>
-      <c r="K11" s="152"/>
-      <c r="L11" s="152"/>
-      <c r="M11" s="152"/>
-      <c r="N11" s="152"/>
-      <c r="O11" s="152"/>
+      <c r="G11" s="153"/>
+      <c r="H11" s="153"/>
+      <c r="I11" s="153"/>
+      <c r="J11" s="153"/>
+      <c r="K11" s="153"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="153"/>
+      <c r="N11" s="153"/>
+      <c r="O11" s="153"/>
     </row>
     <row r="12" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
       <c r="F12" s="72" t="s">
@@ -25030,74 +25030,74 @@
       <c r="O52" s="89"/>
     </row>
     <row r="53" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F53" s="152" t="s">
+      <c r="F53" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="G53" s="152"/>
-      <c r="H53" s="152"/>
-      <c r="I53" s="152"/>
-      <c r="J53" s="152"/>
-      <c r="K53" s="152"/>
-      <c r="L53" s="152"/>
-      <c r="M53" s="152"/>
-      <c r="N53" s="152"/>
-      <c r="O53" s="152"/>
+      <c r="G53" s="153"/>
+      <c r="H53" s="153"/>
+      <c r="I53" s="153"/>
+      <c r="J53" s="153"/>
+      <c r="K53" s="153"/>
+      <c r="L53" s="153"/>
+      <c r="M53" s="153"/>
+      <c r="N53" s="153"/>
+      <c r="O53" s="153"/>
     </row>
     <row r="54" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F54" s="153" t="s">
+      <c r="F54" s="154" t="s">
         <v>320</v>
       </c>
-      <c r="G54" s="152"/>
-      <c r="H54" s="152"/>
-      <c r="I54" s="152"/>
-      <c r="J54" s="152"/>
-      <c r="K54" s="152"/>
-      <c r="L54" s="152"/>
-      <c r="M54" s="152"/>
-      <c r="N54" s="152"/>
-      <c r="O54" s="152"/>
+      <c r="G54" s="153"/>
+      <c r="H54" s="153"/>
+      <c r="I54" s="153"/>
+      <c r="J54" s="153"/>
+      <c r="K54" s="153"/>
+      <c r="L54" s="153"/>
+      <c r="M54" s="153"/>
+      <c r="N54" s="153"/>
+      <c r="O54" s="153"/>
     </row>
     <row r="55" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F55" s="153" t="s">
+      <c r="F55" s="154" t="s">
         <v>321</v>
       </c>
-      <c r="G55" s="152"/>
-      <c r="H55" s="152"/>
-      <c r="I55" s="152"/>
-      <c r="J55" s="152"/>
-      <c r="K55" s="152"/>
-      <c r="L55" s="152"/>
-      <c r="M55" s="152"/>
-      <c r="N55" s="152"/>
-      <c r="O55" s="152"/>
+      <c r="G55" s="153"/>
+      <c r="H55" s="153"/>
+      <c r="I55" s="153"/>
+      <c r="J55" s="153"/>
+      <c r="K55" s="153"/>
+      <c r="L55" s="153"/>
+      <c r="M55" s="153"/>
+      <c r="N55" s="153"/>
+      <c r="O55" s="153"/>
     </row>
     <row r="56" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F56" s="153" t="s">
+      <c r="F56" s="154" t="s">
         <v>655</v>
       </c>
-      <c r="G56" s="152"/>
-      <c r="H56" s="152"/>
-      <c r="I56" s="152"/>
-      <c r="J56" s="152"/>
-      <c r="K56" s="152"/>
-      <c r="L56" s="152"/>
-      <c r="M56" s="152"/>
-      <c r="N56" s="152"/>
-      <c r="O56" s="152"/>
+      <c r="G56" s="153"/>
+      <c r="H56" s="153"/>
+      <c r="I56" s="153"/>
+      <c r="J56" s="153"/>
+      <c r="K56" s="153"/>
+      <c r="L56" s="153"/>
+      <c r="M56" s="153"/>
+      <c r="N56" s="153"/>
+      <c r="O56" s="153"/>
     </row>
     <row r="57" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="F57" s="153" t="s">
+      <c r="F57" s="154" t="s">
         <v>654</v>
       </c>
-      <c r="G57" s="152"/>
-      <c r="H57" s="152"/>
-      <c r="I57" s="152"/>
-      <c r="J57" s="152"/>
-      <c r="K57" s="152"/>
-      <c r="L57" s="152"/>
-      <c r="M57" s="152"/>
-      <c r="N57" s="152"/>
-      <c r="O57" s="152"/>
+      <c r="G57" s="153"/>
+      <c r="H57" s="153"/>
+      <c r="I57" s="153"/>
+      <c r="J57" s="153"/>
+      <c r="K57" s="153"/>
+      <c r="L57" s="153"/>
+      <c r="M57" s="153"/>
+      <c r="N57" s="153"/>
+      <c r="O57" s="153"/>
     </row>
     <row r="58" spans="6:15" ht="17.25" x14ac:dyDescent="0.25">
       <c r="F58" s="72" t="s">
@@ -26207,79 +26207,79 @@
       <c r="F102" s="87"/>
     </row>
     <row r="103" spans="4:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D103" s="152" t="s">
+      <c r="D103" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="E103" s="152"/>
-      <c r="F103" s="152"/>
-      <c r="G103" s="152"/>
-      <c r="H103" s="152"/>
-      <c r="I103" s="152"/>
-      <c r="J103" s="152"/>
-      <c r="K103" s="152"/>
-      <c r="L103" s="152"/>
-      <c r="M103" s="152"/>
-      <c r="N103" s="152"/>
+      <c r="E103" s="153"/>
+      <c r="F103" s="153"/>
+      <c r="G103" s="153"/>
+      <c r="H103" s="153"/>
+      <c r="I103" s="153"/>
+      <c r="J103" s="153"/>
+      <c r="K103" s="153"/>
+      <c r="L103" s="153"/>
+      <c r="M103" s="153"/>
+      <c r="N103" s="153"/>
     </row>
     <row r="104" spans="4:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D104" s="153" t="s">
+      <c r="D104" s="154" t="s">
         <v>320</v>
       </c>
-      <c r="E104" s="152"/>
-      <c r="F104" s="152"/>
-      <c r="G104" s="152"/>
-      <c r="H104" s="152"/>
-      <c r="I104" s="152"/>
-      <c r="J104" s="152"/>
-      <c r="K104" s="152"/>
-      <c r="L104" s="152"/>
-      <c r="M104" s="152"/>
-      <c r="N104" s="152"/>
+      <c r="E104" s="153"/>
+      <c r="F104" s="153"/>
+      <c r="G104" s="153"/>
+      <c r="H104" s="153"/>
+      <c r="I104" s="153"/>
+      <c r="J104" s="153"/>
+      <c r="K104" s="153"/>
+      <c r="L104" s="153"/>
+      <c r="M104" s="153"/>
+      <c r="N104" s="153"/>
     </row>
     <row r="105" spans="4:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D105" s="153" t="s">
+      <c r="D105" s="154" t="s">
         <v>321</v>
       </c>
-      <c r="E105" s="152"/>
-      <c r="F105" s="152"/>
-      <c r="G105" s="152"/>
-      <c r="H105" s="152"/>
-      <c r="I105" s="152"/>
-      <c r="J105" s="152"/>
-      <c r="K105" s="152"/>
-      <c r="L105" s="152"/>
-      <c r="M105" s="152"/>
-      <c r="N105" s="152"/>
+      <c r="E105" s="153"/>
+      <c r="F105" s="153"/>
+      <c r="G105" s="153"/>
+      <c r="H105" s="153"/>
+      <c r="I105" s="153"/>
+      <c r="J105" s="153"/>
+      <c r="K105" s="153"/>
+      <c r="L105" s="153"/>
+      <c r="M105" s="153"/>
+      <c r="N105" s="153"/>
     </row>
     <row r="106" spans="4:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D106" s="153" t="s">
+      <c r="D106" s="154" t="s">
         <v>655</v>
       </c>
-      <c r="E106" s="152"/>
-      <c r="F106" s="152"/>
-      <c r="G106" s="152"/>
-      <c r="H106" s="152"/>
-      <c r="I106" s="152"/>
-      <c r="J106" s="152"/>
-      <c r="K106" s="152"/>
-      <c r="L106" s="152"/>
-      <c r="M106" s="152"/>
-      <c r="N106" s="152"/>
+      <c r="E106" s="153"/>
+      <c r="F106" s="153"/>
+      <c r="G106" s="153"/>
+      <c r="H106" s="153"/>
+      <c r="I106" s="153"/>
+      <c r="J106" s="153"/>
+      <c r="K106" s="153"/>
+      <c r="L106" s="153"/>
+      <c r="M106" s="153"/>
+      <c r="N106" s="153"/>
     </row>
     <row r="107" spans="4:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D107" s="153" t="s">
+      <c r="D107" s="154" t="s">
         <v>397</v>
       </c>
-      <c r="E107" s="152"/>
-      <c r="F107" s="152"/>
-      <c r="G107" s="152"/>
-      <c r="H107" s="152"/>
-      <c r="I107" s="152"/>
-      <c r="J107" s="152"/>
-      <c r="K107" s="152"/>
-      <c r="L107" s="152"/>
-      <c r="M107" s="152"/>
-      <c r="N107" s="152"/>
+      <c r="E107" s="153"/>
+      <c r="F107" s="153"/>
+      <c r="G107" s="153"/>
+      <c r="H107" s="153"/>
+      <c r="I107" s="153"/>
+      <c r="J107" s="153"/>
+      <c r="K107" s="153"/>
+      <c r="L107" s="153"/>
+      <c r="M107" s="153"/>
+      <c r="N107" s="153"/>
     </row>
     <row r="108" spans="4:15" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D108" s="72" t="s">
@@ -26336,7 +26336,7 @@
       <c r="F110" s="76" t="s">
         <v>641</v>
       </c>
-      <c r="G110" s="157" t="s">
+      <c r="G110" s="107" t="s">
         <v>864</v>
       </c>
       <c r="H110" s="76" t="s">
@@ -27475,79 +27475,79 @@
       </c>
     </row>
     <row r="190" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D190" s="152" t="s">
+      <c r="D190" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="E190" s="152"/>
-      <c r="F190" s="152"/>
-      <c r="G190" s="152"/>
-      <c r="H190" s="152"/>
-      <c r="I190" s="152"/>
-      <c r="J190" s="152"/>
-      <c r="K190" s="152"/>
-      <c r="L190" s="152"/>
-      <c r="M190" s="152"/>
-      <c r="N190" s="152"/>
+      <c r="E190" s="153"/>
+      <c r="F190" s="153"/>
+      <c r="G190" s="153"/>
+      <c r="H190" s="153"/>
+      <c r="I190" s="153"/>
+      <c r="J190" s="153"/>
+      <c r="K190" s="153"/>
+      <c r="L190" s="153"/>
+      <c r="M190" s="153"/>
+      <c r="N190" s="153"/>
     </row>
     <row r="191" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D191" s="153" t="s">
+      <c r="D191" s="154" t="s">
         <v>320</v>
       </c>
-      <c r="E191" s="152"/>
-      <c r="F191" s="152"/>
-      <c r="G191" s="152"/>
-      <c r="H191" s="152"/>
-      <c r="I191" s="152"/>
-      <c r="J191" s="152"/>
-      <c r="K191" s="152"/>
-      <c r="L191" s="152"/>
-      <c r="M191" s="152"/>
-      <c r="N191" s="152"/>
+      <c r="E191" s="153"/>
+      <c r="F191" s="153"/>
+      <c r="G191" s="153"/>
+      <c r="H191" s="153"/>
+      <c r="I191" s="153"/>
+      <c r="J191" s="153"/>
+      <c r="K191" s="153"/>
+      <c r="L191" s="153"/>
+      <c r="M191" s="153"/>
+      <c r="N191" s="153"/>
     </row>
     <row r="192" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D192" s="153" t="s">
+      <c r="D192" s="154" t="s">
         <v>321</v>
       </c>
-      <c r="E192" s="152"/>
-      <c r="F192" s="152"/>
-      <c r="G192" s="152"/>
-      <c r="H192" s="152"/>
-      <c r="I192" s="152"/>
-      <c r="J192" s="152"/>
-      <c r="K192" s="152"/>
-      <c r="L192" s="152"/>
-      <c r="M192" s="152"/>
-      <c r="N192" s="152"/>
+      <c r="E192" s="153"/>
+      <c r="F192" s="153"/>
+      <c r="G192" s="153"/>
+      <c r="H192" s="153"/>
+      <c r="I192" s="153"/>
+      <c r="J192" s="153"/>
+      <c r="K192" s="153"/>
+      <c r="L192" s="153"/>
+      <c r="M192" s="153"/>
+      <c r="N192" s="153"/>
     </row>
     <row r="193" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D193" s="153" t="s">
+      <c r="D193" s="154" t="s">
         <v>325</v>
       </c>
-      <c r="E193" s="152"/>
-      <c r="F193" s="152"/>
-      <c r="G193" s="152"/>
-      <c r="H193" s="152"/>
-      <c r="I193" s="152"/>
-      <c r="J193" s="152"/>
-      <c r="K193" s="152"/>
-      <c r="L193" s="152"/>
-      <c r="M193" s="152"/>
-      <c r="N193" s="152"/>
+      <c r="E193" s="153"/>
+      <c r="F193" s="153"/>
+      <c r="G193" s="153"/>
+      <c r="H193" s="153"/>
+      <c r="I193" s="153"/>
+      <c r="J193" s="153"/>
+      <c r="K193" s="153"/>
+      <c r="L193" s="153"/>
+      <c r="M193" s="153"/>
+      <c r="N193" s="153"/>
     </row>
     <row r="194" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D194" s="153" t="s">
+      <c r="D194" s="154" t="s">
         <v>322</v>
       </c>
-      <c r="E194" s="152"/>
-      <c r="F194" s="152"/>
-      <c r="G194" s="152"/>
-      <c r="H194" s="152"/>
-      <c r="I194" s="152"/>
-      <c r="J194" s="152"/>
-      <c r="K194" s="152"/>
-      <c r="L194" s="152"/>
-      <c r="M194" s="152"/>
-      <c r="N194" s="152"/>
+      <c r="E194" s="153"/>
+      <c r="F194" s="153"/>
+      <c r="G194" s="153"/>
+      <c r="H194" s="153"/>
+      <c r="I194" s="153"/>
+      <c r="J194" s="153"/>
+      <c r="K194" s="153"/>
+      <c r="L194" s="153"/>
+      <c r="M194" s="153"/>
+      <c r="N194" s="153"/>
     </row>
     <row r="195" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D195" s="72" t="s">
@@ -28270,34 +28270,34 @@
       </c>
     </row>
     <row r="219" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D219" s="156" t="s">
+      <c r="D219" s="157" t="s">
         <v>332</v>
       </c>
-      <c r="E219" s="154"/>
-      <c r="F219" s="154"/>
-      <c r="G219" s="154"/>
-      <c r="H219" s="154"/>
-      <c r="I219" s="154"/>
-      <c r="J219" s="154"/>
-      <c r="K219" s="154"/>
-      <c r="L219" s="154"/>
-      <c r="M219" s="154"/>
-      <c r="N219" s="154"/>
+      <c r="E219" s="155"/>
+      <c r="F219" s="155"/>
+      <c r="G219" s="155"/>
+      <c r="H219" s="155"/>
+      <c r="I219" s="155"/>
+      <c r="J219" s="155"/>
+      <c r="K219" s="155"/>
+      <c r="L219" s="155"/>
+      <c r="M219" s="155"/>
+      <c r="N219" s="155"/>
     </row>
     <row r="220" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D220" s="154" t="s">
+      <c r="D220" s="155" t="s">
         <v>323</v>
       </c>
-      <c r="E220" s="155"/>
-      <c r="F220" s="155"/>
-      <c r="G220" s="155"/>
-      <c r="H220" s="155"/>
-      <c r="I220" s="155"/>
-      <c r="J220" s="155"/>
-      <c r="K220" s="155"/>
-      <c r="L220" s="155"/>
-      <c r="M220" s="155"/>
-      <c r="N220" s="155"/>
+      <c r="E220" s="156"/>
+      <c r="F220" s="156"/>
+      <c r="G220" s="156"/>
+      <c r="H220" s="156"/>
+      <c r="I220" s="156"/>
+      <c r="J220" s="156"/>
+      <c r="K220" s="156"/>
+      <c r="L220" s="156"/>
+      <c r="M220" s="156"/>
+      <c r="N220" s="156"/>
     </row>
     <row r="221" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D221" s="72" t="s">
@@ -28626,34 +28626,34 @@
       <c r="N234" s="75"/>
     </row>
     <row r="235" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D235" s="156" t="s">
+      <c r="D235" s="157" t="s">
         <v>332</v>
       </c>
-      <c r="E235" s="155"/>
-      <c r="F235" s="155"/>
-      <c r="G235" s="155"/>
-      <c r="H235" s="155"/>
-      <c r="I235" s="155"/>
-      <c r="J235" s="155"/>
-      <c r="K235" s="155"/>
-      <c r="L235" s="155"/>
-      <c r="M235" s="155"/>
-      <c r="N235" s="155"/>
+      <c r="E235" s="156"/>
+      <c r="F235" s="156"/>
+      <c r="G235" s="156"/>
+      <c r="H235" s="156"/>
+      <c r="I235" s="156"/>
+      <c r="J235" s="156"/>
+      <c r="K235" s="156"/>
+      <c r="L235" s="156"/>
+      <c r="M235" s="156"/>
+      <c r="N235" s="156"/>
     </row>
     <row r="236" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="D236" s="156" t="s">
+      <c r="D236" s="157" t="s">
         <v>324</v>
       </c>
-      <c r="E236" s="155"/>
-      <c r="F236" s="155"/>
-      <c r="G236" s="155"/>
-      <c r="H236" s="155"/>
-      <c r="I236" s="155"/>
-      <c r="J236" s="155"/>
-      <c r="K236" s="155"/>
-      <c r="L236" s="155"/>
-      <c r="M236" s="155"/>
-      <c r="N236" s="155"/>
+      <c r="E236" s="156"/>
+      <c r="F236" s="156"/>
+      <c r="G236" s="156"/>
+      <c r="H236" s="156"/>
+      <c r="I236" s="156"/>
+      <c r="J236" s="156"/>
+      <c r="K236" s="156"/>
+      <c r="L236" s="156"/>
+      <c r="M236" s="156"/>
+      <c r="N236" s="156"/>
     </row>
     <row r="237" spans="4:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D237" s="72" t="s">
@@ -29429,6 +29429,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D104:N104"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="F8:O8"/>
+    <mergeCell ref="F9:O9"/>
+    <mergeCell ref="F10:O10"/>
+    <mergeCell ref="F11:O11"/>
+    <mergeCell ref="F53:O53"/>
+    <mergeCell ref="F54:O54"/>
+    <mergeCell ref="F55:O55"/>
+    <mergeCell ref="F56:O56"/>
+    <mergeCell ref="F57:O57"/>
+    <mergeCell ref="D103:N103"/>
     <mergeCell ref="D236:N236"/>
     <mergeCell ref="D105:N105"/>
     <mergeCell ref="D106:N106"/>
@@ -29441,18 +29453,6 @@
     <mergeCell ref="D219:N219"/>
     <mergeCell ref="D220:N220"/>
     <mergeCell ref="D235:N235"/>
-    <mergeCell ref="D104:N104"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="F8:O8"/>
-    <mergeCell ref="F9:O9"/>
-    <mergeCell ref="F10:O10"/>
-    <mergeCell ref="F11:O11"/>
-    <mergeCell ref="F53:O53"/>
-    <mergeCell ref="F54:O54"/>
-    <mergeCell ref="F55:O55"/>
-    <mergeCell ref="F56:O56"/>
-    <mergeCell ref="F57:O57"/>
-    <mergeCell ref="D103:N103"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -29477,64 +29477,64 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="114" t="s">
+      <c r="B3" s="115" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="115" t="s">
+      <c r="B5" s="116" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="114"/>
-      <c r="L5" s="114"/>
-      <c r="M5" s="114"/>
-      <c r="N5" s="114"/>
-      <c r="O5" s="114"/>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
+      <c r="P5" s="115"/>
+      <c r="Q5" s="115"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
@@ -29824,40 +29824,40 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="126" t="s">
         <v>209</v>
       </c>
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
     </row>
     <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="126" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
     </row>
     <row r="5" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="126" t="s">
         <v>211</v>
       </c>
-      <c r="B5" s="125"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="40"/>
@@ -29889,10 +29889,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="116">
+      <c r="B8" s="117">
         <v>45139</v>
       </c>
-      <c r="C8" s="119" t="s">
+      <c r="C8" s="120" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="32" t="s">
@@ -29901,7 +29901,7 @@
       <c r="E8" s="41">
         <v>4</v>
       </c>
-      <c r="F8" s="119" t="s">
+      <c r="F8" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="32" t="s">
@@ -29912,15 +29912,15 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
-      <c r="C9" s="120"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="121"/>
       <c r="D9" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="32">
         <v>0</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="121"/>
       <c r="G9" s="32" t="s">
         <v>32</v>
       </c>
@@ -29929,15 +29929,15 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
-      <c r="C10" s="120"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="121"/>
       <c r="D10" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="32">
         <v>0</v>
       </c>
-      <c r="F10" s="120"/>
+      <c r="F10" s="121"/>
       <c r="G10" s="32" t="s">
         <v>33</v>
       </c>
@@ -29946,15 +29946,15 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="118"/>
-      <c r="C11" s="121"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="122"/>
       <c r="D11" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="32">
         <v>0</v>
       </c>
-      <c r="F11" s="121"/>
+      <c r="F11" s="122"/>
       <c r="G11" s="32" t="s">
         <v>34</v>
       </c>
@@ -29982,10 +29982,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="126">
+      <c r="B13" s="127">
         <v>45192</v>
       </c>
-      <c r="C13" s="119" t="s">
+      <c r="C13" s="120" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="32" t="s">
@@ -29994,7 +29994,7 @@
       <c r="E13" s="32">
         <v>6</v>
       </c>
-      <c r="F13" s="119" t="s">
+      <c r="F13" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="32" t="s">
@@ -30005,15 +30005,15 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="127"/>
-      <c r="C14" s="120"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="32">
         <v>0</v>
       </c>
-      <c r="F14" s="120"/>
+      <c r="F14" s="121"/>
       <c r="G14" s="32" t="s">
         <v>32</v>
       </c>
@@ -30022,26 +30022,26 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="127"/>
-      <c r="C15" s="120"/>
+      <c r="B15" s="128"/>
+      <c r="C15" s="121"/>
       <c r="D15" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E15" s="32"/>
-      <c r="F15" s="120"/>
+      <c r="F15" s="121"/>
       <c r="G15" s="32" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="32"/>
     </row>
     <row r="16" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="128"/>
-      <c r="C16" s="121"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="122"/>
       <c r="D16" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="32"/>
-      <c r="F16" s="121"/>
+      <c r="F16" s="122"/>
       <c r="G16" s="32" t="s">
         <v>34</v>
       </c>
@@ -30067,10 +30067,10 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="116">
+      <c r="B18" s="117">
         <v>45200</v>
       </c>
-      <c r="C18" s="122" t="s">
+      <c r="C18" s="123" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="32" t="s">
@@ -30079,7 +30079,7 @@
       <c r="E18" s="41">
         <v>4</v>
       </c>
-      <c r="F18" s="119" t="s">
+      <c r="F18" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G18" s="32" t="s">
@@ -30090,39 +30090,39 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
-      <c r="C19" s="123"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="124"/>
       <c r="D19" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="32"/>
-      <c r="F19" s="120"/>
+      <c r="F19" s="121"/>
       <c r="G19" s="32" t="s">
         <v>32</v>
       </c>
       <c r="H19" s="32"/>
     </row>
     <row r="20" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="117"/>
-      <c r="C20" s="123"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="124"/>
       <c r="D20" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="41"/>
-      <c r="F20" s="120"/>
+      <c r="F20" s="121"/>
       <c r="G20" s="32" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="32"/>
     </row>
     <row r="21" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="118"/>
-      <c r="C21" s="124"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="125"/>
       <c r="D21" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E21" s="32"/>
-      <c r="F21" s="121"/>
+      <c r="F21" s="122"/>
       <c r="G21" s="32" t="s">
         <v>34</v>
       </c>
@@ -30148,10 +30148,10 @@
       </c>
     </row>
     <row r="23" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="116">
+      <c r="B23" s="117">
         <v>45254</v>
       </c>
-      <c r="C23" s="119" t="s">
+      <c r="C23" s="120" t="s">
         <v>29</v>
       </c>
       <c r="D23" s="32" t="s">
@@ -30160,7 +30160,7 @@
       <c r="E23" s="41">
         <v>4</v>
       </c>
-      <c r="F23" s="119" t="s">
+      <c r="F23" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G23" s="32" t="s">
@@ -30171,15 +30171,15 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="117"/>
-      <c r="C24" s="120"/>
+      <c r="B24" s="118"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E24" s="32">
         <v>0</v>
       </c>
-      <c r="F24" s="120"/>
+      <c r="F24" s="121"/>
       <c r="G24" s="32" t="s">
         <v>32</v>
       </c>
@@ -30188,15 +30188,15 @@
       </c>
     </row>
     <row r="25" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="117"/>
-      <c r="C25" s="120"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="121"/>
       <c r="D25" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E25" s="32">
         <v>0</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="121"/>
       <c r="G25" s="32" t="s">
         <v>33</v>
       </c>
@@ -30205,15 +30205,15 @@
       </c>
     </row>
     <row r="26" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="118"/>
-      <c r="C26" s="121"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="122"/>
       <c r="D26" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E26" s="32">
         <v>0</v>
       </c>
-      <c r="F26" s="121"/>
+      <c r="F26" s="122"/>
       <c r="G26" s="32" t="s">
         <v>34</v>
       </c>
@@ -30241,10 +30241,10 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="116">
+      <c r="B28" s="117">
         <v>45261</v>
       </c>
-      <c r="C28" s="119" t="s">
+      <c r="C28" s="120" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="32" t="s">
@@ -30253,7 +30253,7 @@
       <c r="E28" s="41">
         <v>2</v>
       </c>
-      <c r="F28" s="119" t="s">
+      <c r="F28" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G28" s="32" t="s">
@@ -30264,15 +30264,15 @@
       </c>
     </row>
     <row r="29" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="117"/>
-      <c r="C29" s="120"/>
+      <c r="B29" s="118"/>
+      <c r="C29" s="121"/>
       <c r="D29" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="32">
         <v>0</v>
       </c>
-      <c r="F29" s="120"/>
+      <c r="F29" s="121"/>
       <c r="G29" s="32" t="s">
         <v>32</v>
       </c>
@@ -30281,15 +30281,15 @@
       </c>
     </row>
     <row r="30" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="117"/>
-      <c r="C30" s="120"/>
+      <c r="B30" s="118"/>
+      <c r="C30" s="121"/>
       <c r="D30" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E30" s="32">
         <v>0</v>
       </c>
-      <c r="F30" s="120"/>
+      <c r="F30" s="121"/>
       <c r="G30" s="32" t="s">
         <v>33</v>
       </c>
@@ -30298,15 +30298,15 @@
       </c>
     </row>
     <row r="31" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="118"/>
-      <c r="C31" s="121"/>
+      <c r="B31" s="119"/>
+      <c r="C31" s="122"/>
       <c r="D31" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="32">
         <v>0</v>
       </c>
-      <c r="F31" s="121"/>
+      <c r="F31" s="122"/>
       <c r="G31" s="32" t="s">
         <v>34</v>
       </c>
@@ -30334,10 +30334,10 @@
       </c>
     </row>
     <row r="33" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="116">
+      <c r="B33" s="117">
         <v>45292</v>
       </c>
-      <c r="C33" s="119" t="s">
+      <c r="C33" s="120" t="s">
         <v>29</v>
       </c>
       <c r="D33" s="32" t="s">
@@ -30346,7 +30346,7 @@
       <c r="E33" s="41">
         <v>5</v>
       </c>
-      <c r="F33" s="119" t="s">
+      <c r="F33" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G33" s="32" t="s">
@@ -30357,15 +30357,15 @@
       </c>
     </row>
     <row r="34" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="117"/>
-      <c r="C34" s="120"/>
+      <c r="B34" s="118"/>
+      <c r="C34" s="121"/>
       <c r="D34" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E34" s="32">
         <v>0</v>
       </c>
-      <c r="F34" s="120"/>
+      <c r="F34" s="121"/>
       <c r="G34" s="32" t="s">
         <v>32</v>
       </c>
@@ -30374,15 +30374,15 @@
       </c>
     </row>
     <row r="35" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="117"/>
-      <c r="C35" s="120"/>
+      <c r="B35" s="118"/>
+      <c r="C35" s="121"/>
       <c r="D35" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E35" s="32">
         <v>0</v>
       </c>
-      <c r="F35" s="120"/>
+      <c r="F35" s="121"/>
       <c r="G35" s="32" t="s">
         <v>33</v>
       </c>
@@ -30391,15 +30391,15 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="118"/>
-      <c r="C36" s="121"/>
+      <c r="B36" s="119"/>
+      <c r="C36" s="122"/>
       <c r="D36" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E36" s="32">
         <v>0</v>
       </c>
-      <c r="F36" s="121"/>
+      <c r="F36" s="122"/>
       <c r="G36" s="32" t="s">
         <v>34</v>
       </c>
@@ -30427,10 +30427,10 @@
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="116">
+      <c r="B38" s="117">
         <v>45323</v>
       </c>
-      <c r="C38" s="119" t="s">
+      <c r="C38" s="120" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="32" t="s">
@@ -30439,7 +30439,7 @@
       <c r="E38" s="41">
         <v>1</v>
       </c>
-      <c r="F38" s="119" t="s">
+      <c r="F38" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G38" s="32" t="s">
@@ -30450,15 +30450,15 @@
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="117"/>
-      <c r="C39" s="120"/>
+      <c r="B39" s="118"/>
+      <c r="C39" s="121"/>
       <c r="D39" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="32">
         <v>0</v>
       </c>
-      <c r="F39" s="120"/>
+      <c r="F39" s="121"/>
       <c r="G39" s="32" t="s">
         <v>32</v>
       </c>
@@ -30467,15 +30467,15 @@
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="117"/>
-      <c r="C40" s="120"/>
+      <c r="B40" s="118"/>
+      <c r="C40" s="121"/>
       <c r="D40" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E40" s="32">
         <v>0</v>
       </c>
-      <c r="F40" s="120"/>
+      <c r="F40" s="121"/>
       <c r="G40" s="32" t="s">
         <v>33</v>
       </c>
@@ -30484,15 +30484,15 @@
       </c>
     </row>
     <row r="41" spans="2:8" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="118"/>
-      <c r="C41" s="121"/>
+      <c r="B41" s="119"/>
+      <c r="C41" s="122"/>
       <c r="D41" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E41" s="32">
         <v>0</v>
       </c>
-      <c r="F41" s="121"/>
+      <c r="F41" s="122"/>
       <c r="G41" s="32" t="s">
         <v>34</v>
       </c>
@@ -30520,10 +30520,10 @@
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="116">
+      <c r="B43" s="117">
         <v>45352</v>
       </c>
-      <c r="C43" s="119" t="s">
+      <c r="C43" s="120" t="s">
         <v>29</v>
       </c>
       <c r="D43" s="32" t="s">
@@ -30532,7 +30532,7 @@
       <c r="E43" s="41">
         <v>6</v>
       </c>
-      <c r="F43" s="119" t="s">
+      <c r="F43" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G43" s="32" t="s">
@@ -30543,15 +30543,15 @@
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="117"/>
-      <c r="C44" s="120"/>
+      <c r="B44" s="118"/>
+      <c r="C44" s="121"/>
       <c r="D44" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E44" s="32">
         <v>0</v>
       </c>
-      <c r="F44" s="120"/>
+      <c r="F44" s="121"/>
       <c r="G44" s="32" t="s">
         <v>32</v>
       </c>
@@ -30560,15 +30560,15 @@
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="117"/>
-      <c r="C45" s="120"/>
+      <c r="B45" s="118"/>
+      <c r="C45" s="121"/>
       <c r="D45" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E45" s="32">
         <v>0</v>
       </c>
-      <c r="F45" s="120"/>
+      <c r="F45" s="121"/>
       <c r="G45" s="32" t="s">
         <v>33</v>
       </c>
@@ -30577,15 +30577,15 @@
       </c>
     </row>
     <row r="46" spans="2:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="118"/>
-      <c r="C46" s="121"/>
+      <c r="B46" s="119"/>
+      <c r="C46" s="122"/>
       <c r="D46" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E46" s="32">
         <v>0</v>
       </c>
-      <c r="F46" s="121"/>
+      <c r="F46" s="122"/>
       <c r="G46" s="32" t="s">
         <v>34</v>
       </c>
@@ -30613,10 +30613,10 @@
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="116">
+      <c r="B48" s="117">
         <v>45383</v>
       </c>
-      <c r="C48" s="119" t="s">
+      <c r="C48" s="120" t="s">
         <v>29</v>
       </c>
       <c r="D48" s="32" t="s">
@@ -30625,7 +30625,7 @@
       <c r="E48" s="41">
         <v>1</v>
       </c>
-      <c r="F48" s="119" t="s">
+      <c r="F48" s="120" t="s">
         <v>31</v>
       </c>
       <c r="G48" s="32" t="s">
@@ -30636,15 +30636,15 @@
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="117"/>
-      <c r="C49" s="120"/>
+      <c r="B49" s="118"/>
+      <c r="C49" s="121"/>
       <c r="D49" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E49" s="32">
         <v>0</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="121"/>
       <c r="G49" s="32" t="s">
         <v>32</v>
       </c>
@@ -30653,15 +30653,15 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="117"/>
-      <c r="C50" s="120"/>
+      <c r="B50" s="118"/>
+      <c r="C50" s="121"/>
       <c r="D50" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E50" s="32">
         <v>0</v>
       </c>
-      <c r="F50" s="120"/>
+      <c r="F50" s="121"/>
       <c r="G50" s="32" t="s">
         <v>33</v>
       </c>
@@ -30670,15 +30670,15 @@
       </c>
     </row>
     <row r="51" spans="2:8" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="118"/>
-      <c r="C51" s="121"/>
+      <c r="B51" s="119"/>
+      <c r="C51" s="122"/>
       <c r="D51" s="32" t="s">
         <v>34</v>
       </c>
       <c r="E51" s="32">
         <v>0</v>
       </c>
-      <c r="F51" s="121"/>
+      <c r="F51" s="122"/>
       <c r="G51" s="32" t="s">
         <v>34</v>
       </c>
@@ -30688,24 +30688,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="C48:C51"/>
-    <mergeCell ref="F48:F51"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="C33:C36"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="F28:F31"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C8:C11"/>
     <mergeCell ref="C13:C16"/>
@@ -30718,6 +30700,24 @@
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="C48:C51"/>
+    <mergeCell ref="F48:F51"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="F43:F46"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
@@ -30738,15 +30738,15 @@
   <sheetData>
     <row r="2" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="130" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -30899,15 +30899,15 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="131" t="s">
+      <c r="B13" s="132" t="s">
         <v>194</v>
       </c>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C14" s="33" t="s">
@@ -32140,15 +32140,15 @@
   <sheetData>
     <row r="2" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -32176,7 +32176,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="132" t="s">
+      <c r="C4" s="136" t="s">
         <v>54</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -32190,7 +32190,7 @@
       <c r="H4" s="134"/>
     </row>
     <row r="5" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="133"/>
+      <c r="C5" s="137"/>
       <c r="D5" s="1" t="s">
         <v>56</v>
       </c>
@@ -32210,7 +32210,7 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="132" t="s">
+      <c r="C7" s="136" t="s">
         <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -32228,7 +32228,7 @@
       <c r="H7" s="134"/>
     </row>
     <row r="8" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="133"/>
+      <c r="C8" s="137"/>
       <c r="D8" s="1" t="s">
         <v>56</v>
       </c>
@@ -32252,7 +32252,7 @@
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="132" t="s">
+      <c r="C10" s="136" t="s">
         <v>58</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -32270,7 +32270,7 @@
       <c r="H10" s="134"/>
     </row>
     <row r="11" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="133"/>
+      <c r="C11" s="137"/>
       <c r="D11" s="1" t="s">
         <v>56</v>
       </c>
@@ -32294,7 +32294,7 @@
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="132" t="s">
+      <c r="C13" s="136" t="s">
         <v>59</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -32312,7 +32312,7 @@
       <c r="H13" s="134"/>
     </row>
     <row r="14" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="133"/>
+      <c r="C14" s="137"/>
       <c r="D14" s="1" t="s">
         <v>56</v>
       </c>
@@ -32336,7 +32336,7 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="132" t="s">
+      <c r="C16" s="136" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -32354,7 +32354,7 @@
       <c r="H16" s="134"/>
     </row>
     <row r="17" spans="3:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="133"/>
+      <c r="C17" s="137"/>
       <c r="D17" s="1" t="s">
         <v>56</v>
       </c>
@@ -32378,7 +32378,7 @@
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="3:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="132" t="s">
+      <c r="C19" s="136" t="s">
         <v>61</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -32396,7 +32396,7 @@
       <c r="H19" s="134"/>
     </row>
     <row r="20" spans="3:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="133"/>
+      <c r="C20" s="137"/>
       <c r="D20" s="1" t="s">
         <v>56</v>
       </c>
@@ -32418,7 +32418,7 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="3:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="132" t="s">
+      <c r="C22" s="136" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -32436,7 +32436,7 @@
       <c r="H22" s="134"/>
     </row>
     <row r="23" spans="3:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="133"/>
+      <c r="C23" s="137"/>
       <c r="D23" s="1" t="s">
         <v>56</v>
       </c>
@@ -32458,7 +32458,7 @@
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="3:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="132" t="s">
+      <c r="C25" s="136" t="s">
         <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -32476,7 +32476,7 @@
       <c r="H25" s="134"/>
     </row>
     <row r="26" spans="3:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="133"/>
+      <c r="C26" s="137"/>
       <c r="D26" s="1" t="s">
         <v>56</v>
       </c>
@@ -32488,7 +32488,7 @@
       <c r="H26" s="135"/>
     </row>
     <row r="27" spans="3:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="132" t="s">
+      <c r="C27" s="136" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -32506,7 +32506,7 @@
       <c r="H27" s="134"/>
     </row>
     <row r="28" spans="3:8" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="133"/>
+      <c r="C28" s="137"/>
       <c r="D28" s="1" t="s">
         <v>56</v>
       </c>
@@ -32519,6 +32519,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="H25:H26"/>
     <mergeCell ref="H4:H5"/>
@@ -32535,9 +32538,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="C25:C26"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="55"/>
@@ -32557,14 +32557,14 @@
   <sheetData>
     <row r="2" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="138" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -32643,7 +32643,7 @@
         <f t="shared" ref="F6:F10" si="0">SUM(D6:E6)</f>
         <v>37</v>
       </c>
-      <c r="G6" s="138">
+      <c r="G6" s="139">
         <f>(F6+F7+F8+F9+F10)</f>
         <v>111</v>
       </c>
@@ -32662,7 +32662,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="G7" s="139"/>
+      <c r="G7" s="140"/>
     </row>
     <row r="8" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="6" t="s">
@@ -32678,7 +32678,7 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="G8" s="139"/>
+      <c r="G8" s="140"/>
     </row>
     <row r="9" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="6" t="s">
@@ -32694,7 +32694,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="G9" s="139"/>
+      <c r="G9" s="140"/>
     </row>
     <row r="10" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="6" t="s">
@@ -32710,7 +32710,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G10" s="140"/>
+      <c r="G10" s="141"/>
     </row>
     <row r="11" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="11" t="s">
@@ -32756,14 +32756,14 @@
   <sheetData>
     <row r="2" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -32790,7 +32790,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="141" t="s">
+      <c r="C4" s="142" t="s">
         <v>54</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -32805,7 +32805,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="142"/>
+      <c r="C5" s="143"/>
       <c r="D5" s="14" t="s">
         <v>70</v>
       </c>
@@ -32818,7 +32818,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="142"/>
+      <c r="C6" s="143"/>
       <c r="D6" s="5" t="s">
         <v>71</v>
       </c>
@@ -32831,7 +32831,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="142"/>
+      <c r="C7" s="143"/>
       <c r="D7" s="5" t="s">
         <v>72</v>
       </c>
@@ -32842,7 +32842,7 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="142"/>
+      <c r="C8" s="143"/>
       <c r="D8" s="5" t="s">
         <v>73</v>
       </c>
@@ -32851,7 +32851,7 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="141" t="s">
+      <c r="C9" s="142" t="s">
         <v>57</v>
       </c>
       <c r="D9" s="14" t="s">
@@ -32862,7 +32862,7 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="142"/>
+      <c r="C10" s="143"/>
       <c r="D10" s="5" t="s">
         <v>75</v>
       </c>
@@ -32875,7 +32875,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="142"/>
+      <c r="C11" s="143"/>
       <c r="D11" s="5" t="s">
         <v>72</v>
       </c>
@@ -32886,7 +32886,7 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="142"/>
+      <c r="C12" s="143"/>
       <c r="D12" s="5" t="s">
         <v>76</v>
       </c>
@@ -32899,7 +32899,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="141" t="s">
+      <c r="C13" s="142" t="s">
         <v>58</v>
       </c>
       <c r="D13" s="14" t="s">
@@ -32910,7 +32910,7 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="142"/>
+      <c r="C14" s="143"/>
       <c r="D14" s="5" t="s">
         <v>77</v>
       </c>
@@ -32923,7 +32923,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="142"/>
+      <c r="C15" s="143"/>
       <c r="D15" s="5" t="s">
         <v>78</v>
       </c>
@@ -32936,7 +32936,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="142"/>
+      <c r="C16" s="143"/>
       <c r="D16" s="5" t="s">
         <v>72</v>
       </c>
@@ -32947,7 +32947,7 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="141" t="s">
+      <c r="C17" s="142" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="14" t="s">
@@ -32958,7 +32958,7 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="142"/>
+      <c r="C18" s="143"/>
       <c r="D18" s="5" t="s">
         <v>79</v>
       </c>
@@ -32971,7 +32971,7 @@
       </c>
     </row>
     <row r="19" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="142"/>
+      <c r="C19" s="143"/>
       <c r="D19" s="5" t="s">
         <v>80</v>
       </c>
@@ -32980,7 +32980,7 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="142"/>
+      <c r="C20" s="143"/>
       <c r="D20" s="5" t="s">
         <v>72</v>
       </c>
@@ -32991,7 +32991,7 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="141" t="s">
+      <c r="C21" s="142" t="s">
         <v>60</v>
       </c>
       <c r="D21" s="14" t="s">
@@ -33002,7 +33002,7 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="142"/>
+      <c r="C22" s="143"/>
       <c r="D22" s="5" t="s">
         <v>81</v>
       </c>
@@ -33015,7 +33015,7 @@
       </c>
     </row>
     <row r="23" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="142"/>
+      <c r="C23" s="143"/>
       <c r="D23" s="5" t="s">
         <v>82</v>
       </c>
@@ -33026,7 +33026,7 @@
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="142"/>
+      <c r="C24" s="143"/>
       <c r="D24" s="5" t="s">
         <v>83</v>
       </c>
@@ -33039,7 +33039,7 @@
       </c>
     </row>
     <row r="25" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="142"/>
+      <c r="C25" s="143"/>
       <c r="D25" s="5" t="s">
         <v>84</v>
       </c>
@@ -33048,7 +33048,7 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="141" t="s">
+      <c r="C26" s="142" t="s">
         <v>61</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -33061,7 +33061,7 @@
       </c>
     </row>
     <row r="27" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="142"/>
+      <c r="C27" s="143"/>
       <c r="D27" s="14" t="s">
         <v>86</v>
       </c>
@@ -33072,7 +33072,7 @@
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="142"/>
+      <c r="C28" s="143"/>
       <c r="D28" s="14" t="s">
         <v>87</v>
       </c>
@@ -33085,7 +33085,7 @@
       </c>
     </row>
     <row r="29" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="142"/>
+      <c r="C29" s="143"/>
       <c r="D29" s="14" t="s">
         <v>72</v>
       </c>
@@ -33096,7 +33096,7 @@
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="141" t="s">
+      <c r="C30" s="142" t="s">
         <v>62</v>
       </c>
       <c r="D30" s="14" t="s">
@@ -33109,7 +33109,7 @@
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="142"/>
+      <c r="C31" s="143"/>
       <c r="D31" s="5" t="s">
         <v>84</v>
       </c>
@@ -33122,7 +33122,7 @@
       </c>
     </row>
     <row r="32" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="142"/>
+      <c r="C32" s="143"/>
       <c r="D32" s="5" t="s">
         <v>88</v>
       </c>
@@ -33135,7 +33135,7 @@
       </c>
     </row>
     <row r="33" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="143"/>
+      <c r="C33" s="144"/>
       <c r="D33" s="5" t="s">
         <v>72</v>
       </c>
@@ -33146,7 +33146,7 @@
       <c r="G33" s="5"/>
     </row>
     <row r="34" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="141" t="s">
+      <c r="C34" s="142" t="s">
         <v>63</v>
       </c>
       <c r="D34" s="14" t="s">
@@ -33161,7 +33161,7 @@
       </c>
     </row>
     <row r="35" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="142"/>
+      <c r="C35" s="143"/>
       <c r="D35" s="5" t="s">
         <v>72</v>
       </c>
@@ -33187,7 +33187,7 @@
       </c>
     </row>
     <row r="37" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="141" t="s">
+      <c r="C37" s="142" t="s">
         <v>90</v>
       </c>
       <c r="D37" s="14" t="s">
@@ -33198,7 +33198,7 @@
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="142"/>
+      <c r="C38" s="143"/>
       <c r="D38" s="5" t="s">
         <v>92</v>
       </c>
@@ -33207,7 +33207,7 @@
       <c r="G38" s="5"/>
     </row>
     <row r="39" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="142"/>
+      <c r="C39" s="143"/>
       <c r="D39" s="5" t="s">
         <v>93</v>
       </c>
@@ -33216,7 +33216,7 @@
       <c r="G39" s="4"/>
     </row>
     <row r="40" spans="3:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="142"/>
+      <c r="C40" s="143"/>
       <c r="D40" s="14" t="s">
         <v>94</v>
       </c>
@@ -33252,18 +33252,18 @@
   <sheetData>
     <row r="2" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="145" t="s">
         <v>310</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
       <c r="L2" s="18"/>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -33292,21 +33292,21 @@
       <c r="C4" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="145" t="s">
+      <c r="D4" s="146" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="146"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="145" t="s">
+      <c r="E4" s="147"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="146" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="146"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="148" t="s">
+      <c r="H4" s="147"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="149" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="149"/>
-      <c r="L4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="151"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
@@ -33597,18 +33597,18 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="144" t="s">
+      <c r="B15" s="145" t="s">
         <v>311</v>
       </c>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="136"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="136"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="133"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
       <c r="L15" s="18"/>
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33642,21 +33642,21 @@
       <c r="C18" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D18" s="145" t="s">
+      <c r="D18" s="146" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="146"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="145" t="s">
+      <c r="E18" s="147"/>
+      <c r="F18" s="148"/>
+      <c r="G18" s="146" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="146"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="148" t="s">
+      <c r="H18" s="147"/>
+      <c r="I18" s="148"/>
+      <c r="J18" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="K18" s="149"/>
-      <c r="L18" s="150"/>
+      <c r="K18" s="150"/>
+      <c r="L18" s="151"/>
     </row>
     <row r="19" spans="2:12" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="20"/>
@@ -33934,18 +33934,18 @@
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="144" t="s">
+      <c r="B28" s="145" t="s">
         <v>311</v>
       </c>
-      <c r="C28" s="136"/>
-      <c r="D28" s="136"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="136"/>
-      <c r="G28" s="136"/>
-      <c r="H28" s="136"/>
-      <c r="I28" s="136"/>
-      <c r="J28" s="136"/>
-      <c r="K28" s="136"/>
+      <c r="C28" s="133"/>
+      <c r="D28" s="133"/>
+      <c r="E28" s="133"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="133"/>
       <c r="L28" s="18"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
@@ -33979,21 +33979,21 @@
       <c r="C31" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="145" t="s">
+      <c r="D31" s="146" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="146"/>
-      <c r="F31" s="147"/>
-      <c r="G31" s="145" t="s">
+      <c r="E31" s="147"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="146" t="s">
         <v>63</v>
       </c>
-      <c r="H31" s="146"/>
-      <c r="I31" s="147"/>
-      <c r="J31" s="148" t="s">
+      <c r="H31" s="147"/>
+      <c r="I31" s="148"/>
+      <c r="J31" s="149" t="s">
         <v>89</v>
       </c>
-      <c r="K31" s="149"/>
-      <c r="L31" s="150"/>
+      <c r="K31" s="150"/>
+      <c r="L31" s="151"/>
     </row>
     <row r="32" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="20"/>
@@ -34272,11 +34272,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B15:K15"/>
     <mergeCell ref="B28:K28"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="G31:I31"/>
@@ -34284,6 +34279,11 @@
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="G18:I18"/>
     <mergeCell ref="J18:L18"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B15:K15"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="57"/>
@@ -34303,19 +34303,19 @@
   <sheetData>
     <row r="2" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="133" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="136"/>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="136"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
@@ -34368,7 +34368,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="151" t="s">
+      <c r="B5" s="152" t="s">
         <v>110</v>
       </c>
       <c r="C5" s="20" t="s">
@@ -34385,7 +34385,7 @@
       <c r="L5" s="20"/>
     </row>
     <row r="6" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="151"/>
+      <c r="B6" s="152"/>
       <c r="C6" s="20" t="s">
         <v>47</v>
       </c>
@@ -34400,7 +34400,7 @@
       <c r="L6" s="20"/>
     </row>
     <row r="7" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="151" t="s">
+      <c r="B7" s="152" t="s">
         <v>111</v>
       </c>
       <c r="C7" s="21" t="s">
@@ -34417,7 +34417,7 @@
       <c r="L7" s="23"/>
     </row>
     <row r="8" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="151"/>
+      <c r="B8" s="152"/>
       <c r="C8" s="21" t="s">
         <v>47</v>
       </c>
@@ -34432,7 +34432,7 @@
       <c r="L8" s="23"/>
     </row>
     <row r="9" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="151" t="s">
+      <c r="B9" s="152" t="s">
         <v>112</v>
       </c>
       <c r="C9" s="21" t="s">
@@ -34449,7 +34449,7 @@
       <c r="L9" s="23"/>
     </row>
     <row r="10" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="151"/>
+      <c r="B10" s="152"/>
       <c r="C10" s="21" t="s">
         <v>47</v>
       </c>
@@ -34464,7 +34464,7 @@
       <c r="L10" s="23"/>
     </row>
     <row r="11" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="151" t="s">
+      <c r="B11" s="152" t="s">
         <v>113</v>
       </c>
       <c r="C11" s="21" t="s">
@@ -34481,7 +34481,7 @@
       <c r="L11" s="23"/>
     </row>
     <row r="12" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="151"/>
+      <c r="B12" s="152"/>
       <c r="C12" s="21" t="s">
         <v>47</v>
       </c>
@@ -34496,7 +34496,7 @@
       <c r="L12" s="23"/>
     </row>
     <row r="13" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="151" t="s">
+      <c r="B13" s="152" t="s">
         <v>114</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -34513,7 +34513,7 @@
       <c r="L13" s="23"/>
     </row>
     <row r="14" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="151"/>
+      <c r="B14" s="152"/>
       <c r="C14" s="21" t="s">
         <v>47</v>
       </c>
@@ -34528,7 +34528,7 @@
       <c r="L14" s="23"/>
     </row>
     <row r="15" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="151" t="s">
+      <c r="B15" s="152" t="s">
         <v>115</v>
       </c>
       <c r="C15" s="21" t="s">
@@ -34545,7 +34545,7 @@
       <c r="L15" s="23"/>
     </row>
     <row r="16" spans="1:15" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="151"/>
+      <c r="B16" s="152"/>
       <c r="C16" s="21" t="s">
         <v>47</v>
       </c>
@@ -34560,7 +34560,7 @@
       <c r="L16" s="23"/>
     </row>
     <row r="17" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="151" t="s">
+      <c r="B17" s="152" t="s">
         <v>116</v>
       </c>
       <c r="C17" s="21" t="s">
@@ -34577,7 +34577,7 @@
       <c r="L17" s="23"/>
     </row>
     <row r="18" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="151"/>
+      <c r="B18" s="152"/>
       <c r="C18" s="21" t="s">
         <v>47</v>
       </c>
@@ -34592,7 +34592,7 @@
       <c r="L18" s="23"/>
     </row>
     <row r="19" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="152" t="s">
         <v>117</v>
       </c>
       <c r="C19" s="21" t="s">
@@ -34609,7 +34609,7 @@
       <c r="L19" s="23"/>
     </row>
     <row r="20" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="151"/>
+      <c r="B20" s="152"/>
       <c r="C20" s="21" t="s">
         <v>47</v>
       </c>
@@ -34624,7 +34624,7 @@
       <c r="L20" s="23"/>
     </row>
     <row r="21" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="151" t="s">
+      <c r="B21" s="152" t="s">
         <v>118</v>
       </c>
       <c r="C21" s="21" t="s">
@@ -34641,7 +34641,7 @@
       <c r="L21" s="23"/>
     </row>
     <row r="22" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="151"/>
+      <c r="B22" s="152"/>
       <c r="C22" s="21" t="s">
         <v>47</v>
       </c>
@@ -34656,7 +34656,7 @@
       <c r="L22" s="23"/>
     </row>
     <row r="23" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="151" t="s">
+      <c r="B23" s="152" t="s">
         <v>119</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -34673,7 +34673,7 @@
       <c r="L23" s="23"/>
     </row>
     <row r="24" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="151"/>
+      <c r="B24" s="152"/>
       <c r="C24" s="21" t="s">
         <v>47</v>
       </c>
@@ -34688,7 +34688,7 @@
       <c r="L24" s="23"/>
     </row>
     <row r="25" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="151" t="s">
+      <c r="B25" s="152" t="s">
         <v>120</v>
       </c>
       <c r="C25" s="21" t="s">
@@ -34705,7 +34705,7 @@
       <c r="L25" s="23"/>
     </row>
     <row r="26" spans="2:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="151"/>
+      <c r="B26" s="152"/>
       <c r="C26" s="21" t="s">
         <v>47</v>
       </c>
@@ -34751,18 +34751,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B13:B14"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="54"/>
